--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -725,25 +725,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>113448700</v>
+        <v>113772800</v>
       </c>
       <c r="E8" s="3">
-        <v>132286500</v>
+        <v>132664400</v>
       </c>
       <c r="F8" s="3">
-        <v>122474800</v>
+        <v>122824700</v>
       </c>
       <c r="G8" s="3">
-        <v>144302800</v>
+        <v>144715100</v>
       </c>
       <c r="H8" s="3">
-        <v>116830600</v>
+        <v>117164400</v>
       </c>
       <c r="I8" s="3">
-        <v>144187800</v>
+        <v>144599800</v>
       </c>
       <c r="J8" s="3">
-        <v>138692300</v>
+        <v>139088600</v>
       </c>
       <c r="K8" s="3">
         <v>122920600</v>
@@ -767,25 +767,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>91353700</v>
+        <v>91614800</v>
       </c>
       <c r="E9" s="3">
-        <v>110113400</v>
+        <v>110428000</v>
       </c>
       <c r="F9" s="3">
-        <v>104429100</v>
+        <v>104727400</v>
       </c>
       <c r="G9" s="3">
-        <v>125564900</v>
+        <v>125923600</v>
       </c>
       <c r="H9" s="3">
-        <v>94422100</v>
+        <v>94691900</v>
       </c>
       <c r="I9" s="3">
-        <v>123754000</v>
+        <v>124107600</v>
       </c>
       <c r="J9" s="3">
-        <v>116685200</v>
+        <v>117018600</v>
       </c>
       <c r="K9" s="3">
         <v>102370000</v>
@@ -809,25 +809,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>22094900</v>
+        <v>22158100</v>
       </c>
       <c r="E10" s="3">
-        <v>22173100</v>
+        <v>22236400</v>
       </c>
       <c r="F10" s="3">
-        <v>18045700</v>
+        <v>18097300</v>
       </c>
       <c r="G10" s="3">
-        <v>18738000</v>
+        <v>18791500</v>
       </c>
       <c r="H10" s="3">
-        <v>22408500</v>
+        <v>22472500</v>
       </c>
       <c r="I10" s="3">
-        <v>20433800</v>
+        <v>20492200</v>
       </c>
       <c r="J10" s="3">
-        <v>22007100</v>
+        <v>22069900</v>
       </c>
       <c r="K10" s="3">
         <v>20550600</v>
@@ -953,25 +953,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1106700</v>
+        <v>1109900</v>
       </c>
       <c r="E14" s="3">
-        <v>481700</v>
+        <v>483100</v>
       </c>
       <c r="F14" s="3">
-        <v>660800</v>
+        <v>662700</v>
       </c>
       <c r="G14" s="3">
-        <v>307100</v>
+        <v>307900</v>
       </c>
       <c r="H14" s="3">
-        <v>8367500</v>
+        <v>8391400</v>
       </c>
       <c r="I14" s="3">
-        <v>449200</v>
+        <v>450500</v>
       </c>
       <c r="J14" s="3">
-        <v>987400</v>
+        <v>990200</v>
       </c>
       <c r="K14" s="3">
         <v>887700</v>
@@ -1052,25 +1052,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>103360400</v>
+        <v>103655700</v>
       </c>
       <c r="E17" s="3">
-        <v>122433600</v>
+        <v>122783400</v>
       </c>
       <c r="F17" s="3">
-        <v>116533300</v>
+        <v>116866300</v>
       </c>
       <c r="G17" s="3">
-        <v>138227900</v>
+        <v>138622900</v>
       </c>
       <c r="H17" s="3">
-        <v>114872200</v>
+        <v>115200400</v>
       </c>
       <c r="I17" s="3">
-        <v>135795300</v>
+        <v>136183300</v>
       </c>
       <c r="J17" s="3">
-        <v>128765600</v>
+        <v>129133500</v>
       </c>
       <c r="K17" s="3">
         <v>114465000</v>
@@ -1094,25 +1094,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10088300</v>
+        <v>10117200</v>
       </c>
       <c r="E18" s="3">
-        <v>9852900</v>
+        <v>9881000</v>
       </c>
       <c r="F18" s="3">
-        <v>5941500</v>
+        <v>5958400</v>
       </c>
       <c r="G18" s="3">
-        <v>6074900</v>
+        <v>6092300</v>
       </c>
       <c r="H18" s="3">
-        <v>1958400</v>
+        <v>1964000</v>
       </c>
       <c r="I18" s="3">
-        <v>8392500</v>
+        <v>8416500</v>
       </c>
       <c r="J18" s="3">
-        <v>9926700</v>
+        <v>9955000</v>
       </c>
       <c r="K18" s="3">
         <v>8455500</v>
@@ -1154,25 +1154,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-120400</v>
+        <v>-120800</v>
       </c>
       <c r="E20" s="3">
-        <v>626000</v>
+        <v>627800</v>
       </c>
       <c r="F20" s="3">
-        <v>297300</v>
+        <v>298100</v>
       </c>
       <c r="G20" s="3">
-        <v>808300</v>
+        <v>810600</v>
       </c>
       <c r="H20" s="3">
-        <v>311400</v>
+        <v>312300</v>
       </c>
       <c r="I20" s="3">
-        <v>288600</v>
+        <v>289400</v>
       </c>
       <c r="J20" s="3">
-        <v>236500</v>
+        <v>237200</v>
       </c>
       <c r="K20" s="3">
         <v>226400</v>
@@ -1199,22 +1199,22 @@
         <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>11422500</v>
+        <v>11461200</v>
       </c>
       <c r="F21" s="3">
-        <v>7514200</v>
+        <v>7543800</v>
       </c>
       <c r="G21" s="3">
-        <v>8375600</v>
+        <v>8409100</v>
       </c>
       <c r="H21" s="3">
-        <v>3190600</v>
+        <v>3205600</v>
       </c>
       <c r="I21" s="3">
-        <v>9148500</v>
+        <v>9177700</v>
       </c>
       <c r="J21" s="3">
-        <v>10892000</v>
+        <v>10927800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1238,25 +1238,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>517500</v>
+        <v>519000</v>
       </c>
       <c r="E22" s="3">
-        <v>501300</v>
+        <v>502700</v>
       </c>
       <c r="F22" s="3">
-        <v>952600</v>
+        <v>955400</v>
       </c>
       <c r="G22" s="3">
-        <v>781200</v>
+        <v>783400</v>
       </c>
       <c r="H22" s="3">
-        <v>609800</v>
+        <v>611500</v>
       </c>
       <c r="I22" s="3">
-        <v>341800</v>
+        <v>342800</v>
       </c>
       <c r="J22" s="3">
-        <v>321200</v>
+        <v>322100</v>
       </c>
       <c r="K22" s="3">
         <v>516300</v>
@@ -1280,25 +1280,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9450400</v>
+        <v>9477400</v>
       </c>
       <c r="E23" s="3">
-        <v>9977700</v>
+        <v>10006200</v>
       </c>
       <c r="F23" s="3">
-        <v>5286100</v>
+        <v>5301200</v>
       </c>
       <c r="G23" s="3">
-        <v>6102000</v>
+        <v>6119500</v>
       </c>
       <c r="H23" s="3">
-        <v>1660100</v>
+        <v>1664800</v>
       </c>
       <c r="I23" s="3">
-        <v>8339300</v>
+        <v>8363100</v>
       </c>
       <c r="J23" s="3">
-        <v>9842000</v>
+        <v>9870200</v>
       </c>
       <c r="K23" s="3">
         <v>8165600</v>
@@ -1322,25 +1322,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2012700</v>
+        <v>2018400</v>
       </c>
       <c r="E24" s="3">
-        <v>1832600</v>
+        <v>1837800</v>
       </c>
       <c r="F24" s="3">
-        <v>1672000</v>
+        <v>1676800</v>
       </c>
       <c r="G24" s="3">
-        <v>1539600</v>
+        <v>1544000</v>
       </c>
       <c r="H24" s="3">
-        <v>1599300</v>
+        <v>1603900</v>
       </c>
       <c r="I24" s="3">
-        <v>1175100</v>
+        <v>1178400</v>
       </c>
       <c r="J24" s="3">
-        <v>2645200</v>
+        <v>2652800</v>
       </c>
       <c r="K24" s="3">
         <v>1899100</v>
@@ -1406,25 +1406,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7437700</v>
+        <v>7458900</v>
       </c>
       <c r="E26" s="3">
-        <v>8145100</v>
+        <v>8168400</v>
       </c>
       <c r="F26" s="3">
-        <v>3614100</v>
+        <v>3624500</v>
       </c>
       <c r="G26" s="3">
-        <v>4562400</v>
+        <v>4575500</v>
       </c>
       <c r="H26" s="3">
-        <v>60800</v>
+        <v>60900</v>
       </c>
       <c r="I26" s="3">
-        <v>7164300</v>
+        <v>7184700</v>
       </c>
       <c r="J26" s="3">
-        <v>7196800</v>
+        <v>7217400</v>
       </c>
       <c r="K26" s="3">
         <v>6266500</v>
@@ -1448,25 +1448,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7044900</v>
+        <v>7065000</v>
       </c>
       <c r="E27" s="3">
-        <v>7703500</v>
+        <v>7725500</v>
       </c>
       <c r="F27" s="3">
-        <v>3240900</v>
+        <v>3250200</v>
       </c>
       <c r="G27" s="3">
-        <v>3936400</v>
+        <v>3947600</v>
       </c>
       <c r="H27" s="3">
-        <v>2502000</v>
+        <v>2509200</v>
       </c>
       <c r="I27" s="3">
-        <v>6488300</v>
+        <v>6506800</v>
       </c>
       <c r="J27" s="3">
-        <v>6511100</v>
+        <v>6529700</v>
       </c>
       <c r="K27" s="3">
         <v>5552400</v>
@@ -1541,16 +1541,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-26000</v>
+        <v>-26100</v>
       </c>
       <c r="H29" s="3">
-        <v>-464400</v>
+        <v>-465700</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-476300</v>
+        <v>-477700</v>
       </c>
       <c r="K29" s="3">
         <v>67700</v>
@@ -1658,25 +1658,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>120400</v>
+        <v>120800</v>
       </c>
       <c r="E32" s="3">
-        <v>-626000</v>
+        <v>-627800</v>
       </c>
       <c r="F32" s="3">
-        <v>-297300</v>
+        <v>-298100</v>
       </c>
       <c r="G32" s="3">
-        <v>-808300</v>
+        <v>-810600</v>
       </c>
       <c r="H32" s="3">
-        <v>-311400</v>
+        <v>-312300</v>
       </c>
       <c r="I32" s="3">
-        <v>-288600</v>
+        <v>-289400</v>
       </c>
       <c r="J32" s="3">
-        <v>-236500</v>
+        <v>-237200</v>
       </c>
       <c r="K32" s="3">
         <v>-226400</v>
@@ -1700,25 +1700,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7044900</v>
+        <v>7065000</v>
       </c>
       <c r="E33" s="3">
-        <v>7703500</v>
+        <v>7725500</v>
       </c>
       <c r="F33" s="3">
-        <v>3240900</v>
+        <v>3250200</v>
       </c>
       <c r="G33" s="3">
-        <v>3910300</v>
+        <v>3921500</v>
       </c>
       <c r="H33" s="3">
-        <v>2037600</v>
+        <v>2043500</v>
       </c>
       <c r="I33" s="3">
-        <v>6488300</v>
+        <v>6506800</v>
       </c>
       <c r="J33" s="3">
-        <v>6034800</v>
+        <v>6052000</v>
       </c>
       <c r="K33" s="3">
         <v>5620100</v>
@@ -1784,25 +1784,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7044900</v>
+        <v>7065000</v>
       </c>
       <c r="E35" s="3">
-        <v>7703500</v>
+        <v>7725500</v>
       </c>
       <c r="F35" s="3">
-        <v>3240900</v>
+        <v>3250200</v>
       </c>
       <c r="G35" s="3">
-        <v>3910300</v>
+        <v>3921500</v>
       </c>
       <c r="H35" s="3">
-        <v>2037600</v>
+        <v>2043500</v>
       </c>
       <c r="I35" s="3">
-        <v>6488300</v>
+        <v>6506800</v>
       </c>
       <c r="J35" s="3">
-        <v>6034800</v>
+        <v>6052000</v>
       </c>
       <c r="K35" s="3">
         <v>5620100</v>
@@ -1909,25 +1909,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>28391200</v>
+        <v>28472300</v>
       </c>
       <c r="E41" s="3">
-        <v>27180300</v>
+        <v>27258000</v>
       </c>
       <c r="F41" s="3">
-        <v>30637100</v>
+        <v>30724700</v>
       </c>
       <c r="G41" s="3">
-        <v>23813600</v>
+        <v>23881600</v>
       </c>
       <c r="H41" s="3">
-        <v>33992000</v>
+        <v>34089100</v>
       </c>
       <c r="I41" s="3">
-        <v>25929300</v>
+        <v>26003400</v>
       </c>
       <c r="J41" s="3">
-        <v>28550700</v>
+        <v>28632300</v>
       </c>
       <c r="K41" s="3">
         <v>27799000</v>
@@ -1993,25 +1993,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>44393900</v>
+        <v>44520700</v>
       </c>
       <c r="E43" s="3">
-        <v>40595300</v>
+        <v>40711300</v>
       </c>
       <c r="F43" s="3">
-        <v>40861100</v>
+        <v>40977800</v>
       </c>
       <c r="G43" s="3">
-        <v>42846700</v>
+        <v>42969100</v>
       </c>
       <c r="H43" s="3">
-        <v>45514700</v>
+        <v>45644700</v>
       </c>
       <c r="I43" s="3">
-        <v>32811500</v>
+        <v>32905200</v>
       </c>
       <c r="J43" s="3">
-        <v>37796000</v>
+        <v>37904000</v>
       </c>
       <c r="K43" s="3">
         <v>33546000</v>
@@ -2161,25 +2161,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>503523000</v>
+        <v>504961000</v>
       </c>
       <c r="E47" s="3">
-        <v>553135000</v>
+        <v>554716000</v>
       </c>
       <c r="F47" s="3">
-        <v>578128000</v>
+        <v>579780000</v>
       </c>
       <c r="G47" s="3">
-        <v>564786000</v>
+        <v>566400000</v>
       </c>
       <c r="H47" s="3">
-        <v>619904000</v>
+        <v>621675000</v>
       </c>
       <c r="I47" s="3">
-        <v>601346000</v>
+        <v>603064000</v>
       </c>
       <c r="J47" s="3">
-        <v>618072000</v>
+        <v>619838000</v>
       </c>
       <c r="K47" s="3">
         <v>572538000</v>
@@ -2203,25 +2203,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>33542800</v>
+        <v>33638600</v>
       </c>
       <c r="E48" s="3">
-        <v>33415800</v>
+        <v>33511300</v>
       </c>
       <c r="F48" s="3">
-        <v>30949600</v>
+        <v>31038100</v>
       </c>
       <c r="G48" s="3">
-        <v>28397700</v>
+        <v>28478800</v>
       </c>
       <c r="H48" s="3">
-        <v>24453700</v>
+        <v>24523600</v>
       </c>
       <c r="I48" s="3">
-        <v>26561900</v>
+        <v>26637800</v>
       </c>
       <c r="J48" s="3">
-        <v>24837800</v>
+        <v>24908800</v>
       </c>
       <c r="K48" s="3">
         <v>23065500</v>
@@ -2245,25 +2245,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>48305300</v>
+        <v>48443300</v>
       </c>
       <c r="E49" s="3">
-        <v>23288400</v>
+        <v>23355000</v>
       </c>
       <c r="F49" s="3">
-        <v>22801300</v>
+        <v>22866400</v>
       </c>
       <c r="G49" s="3">
-        <v>24573100</v>
+        <v>24643300</v>
       </c>
       <c r="H49" s="3">
-        <v>23666000</v>
+        <v>23733600</v>
       </c>
       <c r="I49" s="3">
-        <v>20138700</v>
+        <v>20196200</v>
       </c>
       <c r="J49" s="3">
-        <v>21646800</v>
+        <v>21708700</v>
       </c>
       <c r="K49" s="3">
         <v>21518700</v>
@@ -2371,25 +2371,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18905000</v>
+        <v>18959100</v>
       </c>
       <c r="E52" s="3">
-        <v>9692300</v>
+        <v>9720000</v>
       </c>
       <c r="F52" s="3">
-        <v>36635000</v>
+        <v>36739700</v>
       </c>
       <c r="G52" s="3">
-        <v>39324700</v>
+        <v>39437100</v>
       </c>
       <c r="H52" s="3">
-        <v>29619400</v>
+        <v>29704000</v>
       </c>
       <c r="I52" s="3">
-        <v>6353800</v>
+        <v>6371900</v>
       </c>
       <c r="J52" s="3">
-        <v>2730900</v>
+        <v>2738700</v>
       </c>
       <c r="K52" s="3">
         <v>5365100</v>
@@ -2455,25 +2455,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>691020000</v>
+        <v>692995000</v>
       </c>
       <c r="E54" s="3">
-        <v>841408000</v>
+        <v>843812000</v>
       </c>
       <c r="F54" s="3">
-        <v>872979000</v>
+        <v>875473000</v>
       </c>
       <c r="G54" s="3">
-        <v>847253000</v>
+        <v>849673000</v>
       </c>
       <c r="H54" s="3">
-        <v>1009800000</v>
+        <v>1012690000</v>
       </c>
       <c r="I54" s="3">
-        <v>944089000</v>
+        <v>946786000</v>
       </c>
       <c r="J54" s="3">
-        <v>968670000</v>
+        <v>971437000</v>
       </c>
       <c r="K54" s="3">
         <v>938520000</v>
@@ -2575,25 +2575,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1230400</v>
+        <v>1233900</v>
       </c>
       <c r="E58" s="3">
-        <v>1371400</v>
+        <v>1375400</v>
       </c>
       <c r="F58" s="3">
-        <v>1746800</v>
+        <v>1751800</v>
       </c>
       <c r="G58" s="3">
-        <v>756200</v>
+        <v>758400</v>
       </c>
       <c r="H58" s="3">
-        <v>1546100</v>
+        <v>1550500</v>
       </c>
       <c r="I58" s="3">
-        <v>2523700</v>
+        <v>2530900</v>
       </c>
       <c r="J58" s="3">
-        <v>4095900</v>
+        <v>4107600</v>
       </c>
       <c r="K58" s="3">
         <v>3477600</v>
@@ -2617,25 +2617,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>737150000</v>
+        <v>739256000</v>
       </c>
       <c r="E59" s="3">
-        <v>220282000</v>
+        <v>220912000</v>
       </c>
       <c r="F59" s="3">
-        <v>205165000</v>
+        <v>205751000</v>
       </c>
       <c r="G59" s="3">
-        <v>194368000</v>
+        <v>194923000</v>
       </c>
       <c r="H59" s="3">
-        <v>313829000</v>
+        <v>314725000</v>
       </c>
       <c r="I59" s="3">
-        <v>320000000</v>
+        <v>320914000</v>
       </c>
       <c r="J59" s="3">
-        <v>321515000</v>
+        <v>322433000</v>
       </c>
       <c r="K59" s="3">
         <v>335035000</v>
@@ -2701,25 +2701,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26241800</v>
+        <v>26316800</v>
       </c>
       <c r="E61" s="3">
-        <v>23050800</v>
+        <v>23116700</v>
       </c>
       <c r="F61" s="3">
-        <v>22604900</v>
+        <v>22669500</v>
       </c>
       <c r="G61" s="3">
-        <v>26933000</v>
+        <v>27009900</v>
       </c>
       <c r="H61" s="3">
-        <v>27114100</v>
+        <v>27191600</v>
       </c>
       <c r="I61" s="3">
-        <v>10322700</v>
+        <v>10352200</v>
       </c>
       <c r="J61" s="3">
-        <v>9171500</v>
+        <v>9197700</v>
       </c>
       <c r="K61" s="3">
         <v>8186800</v>
@@ -2743,25 +2743,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>988400</v>
+        <v>991300</v>
       </c>
       <c r="E62" s="3">
-        <v>5787400</v>
+        <v>5803900</v>
       </c>
       <c r="F62" s="3">
-        <v>16188200</v>
+        <v>16234500</v>
       </c>
       <c r="G62" s="3">
-        <v>15463400</v>
+        <v>15507600</v>
       </c>
       <c r="H62" s="3">
-        <v>14470600</v>
+        <v>14512000</v>
       </c>
       <c r="I62" s="3">
-        <v>16122000</v>
+        <v>16168100</v>
       </c>
       <c r="J62" s="3">
-        <v>18363600</v>
+        <v>18416100</v>
       </c>
       <c r="K62" s="3">
         <v>16430700</v>
@@ -2911,25 +2911,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>641033000</v>
+        <v>642865000</v>
       </c>
       <c r="E66" s="3">
-        <v>764226000</v>
+        <v>766410000</v>
       </c>
       <c r="F66" s="3">
-        <v>795281000</v>
+        <v>797553000</v>
       </c>
       <c r="G66" s="3">
-        <v>771414000</v>
+        <v>773618000</v>
       </c>
       <c r="H66" s="3">
-        <v>942070000</v>
+        <v>944761000</v>
       </c>
       <c r="I66" s="3">
-        <v>868561000</v>
+        <v>871043000</v>
       </c>
       <c r="J66" s="3">
-        <v>892072000</v>
+        <v>894621000</v>
       </c>
       <c r="K66" s="3">
         <v>866074000</v>
@@ -3139,25 +3139,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>69348900</v>
+        <v>69547000</v>
       </c>
       <c r="E72" s="3">
-        <v>33986500</v>
+        <v>34083600</v>
       </c>
       <c r="F72" s="3">
-        <v>53448200</v>
+        <v>53600900</v>
       </c>
       <c r="G72" s="3">
-        <v>49107100</v>
+        <v>49247400</v>
       </c>
       <c r="H72" s="3">
-        <v>41351500</v>
+        <v>41469700</v>
       </c>
       <c r="I72" s="3">
-        <v>52170100</v>
+        <v>52319100</v>
       </c>
       <c r="J72" s="3">
-        <v>47846300</v>
+        <v>47983000</v>
       </c>
       <c r="K72" s="3">
         <v>30534900</v>
@@ -3307,25 +3307,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>49987000</v>
+        <v>50129900</v>
       </c>
       <c r="E76" s="3">
-        <v>77181500</v>
+        <v>77402000</v>
       </c>
       <c r="F76" s="3">
-        <v>77697900</v>
+        <v>77919900</v>
       </c>
       <c r="G76" s="3">
-        <v>75838200</v>
+        <v>76054900</v>
       </c>
       <c r="H76" s="3">
-        <v>67734400</v>
+        <v>67927900</v>
       </c>
       <c r="I76" s="3">
-        <v>75527900</v>
+        <v>75743700</v>
       </c>
       <c r="J76" s="3">
-        <v>76597700</v>
+        <v>76816600</v>
       </c>
       <c r="K76" s="3">
         <v>72446600</v>
@@ -3438,25 +3438,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7044900</v>
+        <v>7065000</v>
       </c>
       <c r="E81" s="3">
-        <v>7703500</v>
+        <v>7725500</v>
       </c>
       <c r="F81" s="3">
-        <v>3240900</v>
+        <v>3250200</v>
       </c>
       <c r="G81" s="3">
-        <v>3910300</v>
+        <v>3921500</v>
       </c>
       <c r="H81" s="3">
-        <v>2037600</v>
+        <v>2043500</v>
       </c>
       <c r="I81" s="3">
-        <v>6488300</v>
+        <v>6506800</v>
       </c>
       <c r="J81" s="3">
-        <v>6034800</v>
+        <v>6052000</v>
       </c>
       <c r="K81" s="3">
         <v>5620100</v>
@@ -3501,22 +3501,22 @@
         <v>8</v>
       </c>
       <c r="E83" s="3">
-        <v>944000</v>
+        <v>946600</v>
       </c>
       <c r="F83" s="3">
-        <v>1276000</v>
+        <v>1279600</v>
       </c>
       <c r="G83" s="3">
-        <v>1493000</v>
+        <v>1497200</v>
       </c>
       <c r="H83" s="3">
-        <v>921200</v>
+        <v>923800</v>
       </c>
       <c r="I83" s="3">
-        <v>467600</v>
+        <v>469000</v>
       </c>
       <c r="J83" s="3">
-        <v>729100</v>
+        <v>731200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3750,25 +3750,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8021400</v>
+        <v>8044300</v>
       </c>
       <c r="E89" s="3">
-        <v>10781600</v>
+        <v>10812400</v>
       </c>
       <c r="F89" s="3">
-        <v>24556800</v>
+        <v>24627000</v>
       </c>
       <c r="G89" s="3">
-        <v>8601900</v>
+        <v>8626500</v>
       </c>
       <c r="H89" s="3">
-        <v>8282900</v>
+        <v>8306600</v>
       </c>
       <c r="I89" s="3">
-        <v>17929600</v>
+        <v>17980900</v>
       </c>
       <c r="J89" s="3">
-        <v>14689800</v>
+        <v>14731800</v>
       </c>
       <c r="K89" s="3">
         <v>13659800</v>
@@ -3810,25 +3810,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-383000</v>
+        <v>-384100</v>
       </c>
       <c r="E91" s="3">
-        <v>-379800</v>
+        <v>-380800</v>
       </c>
       <c r="F91" s="3">
-        <v>-422100</v>
+        <v>-423300</v>
       </c>
       <c r="G91" s="3">
-        <v>-501300</v>
+        <v>-502700</v>
       </c>
       <c r="H91" s="3">
-        <v>-501300</v>
+        <v>-502700</v>
       </c>
       <c r="I91" s="3">
-        <v>-426400</v>
+        <v>-427600</v>
       </c>
       <c r="J91" s="3">
-        <v>-512100</v>
+        <v>-513600</v>
       </c>
       <c r="K91" s="3">
         <v>-373500</v>
@@ -3936,25 +3936,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>510000</v>
+        <v>511400</v>
       </c>
       <c r="E94" s="3">
-        <v>-9711800</v>
+        <v>-9739600</v>
       </c>
       <c r="F94" s="3">
-        <v>-12402600</v>
+        <v>-12438100</v>
       </c>
       <c r="G94" s="3">
-        <v>-11979500</v>
+        <v>-12013700</v>
       </c>
       <c r="H94" s="3">
-        <v>-2304500</v>
+        <v>-2311100</v>
       </c>
       <c r="I94" s="3">
-        <v>-13385600</v>
+        <v>-13423900</v>
       </c>
       <c r="J94" s="3">
-        <v>-11141900</v>
+        <v>-11173700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3996,25 +3996,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3988500</v>
+        <v>-3999900</v>
       </c>
       <c r="E96" s="3">
-        <v>-3785600</v>
+        <v>-3796400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1891200</v>
+        <v>-1896600</v>
       </c>
       <c r="G96" s="3">
-        <v>-3545800</v>
+        <v>-3555900</v>
       </c>
       <c r="H96" s="3">
-        <v>-3704200</v>
+        <v>-3714800</v>
       </c>
       <c r="I96" s="3">
-        <v>-3361300</v>
+        <v>-3370900</v>
       </c>
       <c r="J96" s="3">
-        <v>-3171500</v>
+        <v>-3180500</v>
       </c>
       <c r="K96" s="3">
         <v>-2364600</v>
@@ -4164,25 +4164,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-6644500</v>
+        <v>-6663500</v>
       </c>
       <c r="E100" s="3">
-        <v>-4701300</v>
+        <v>-4714700</v>
       </c>
       <c r="F100" s="3">
-        <v>-5345800</v>
+        <v>-5361100</v>
       </c>
       <c r="G100" s="3">
-        <v>-7570000</v>
+        <v>-7591700</v>
       </c>
       <c r="H100" s="3">
-        <v>4252100</v>
+        <v>4264300</v>
       </c>
       <c r="I100" s="3">
-        <v>-6630400</v>
+        <v>-6649400</v>
       </c>
       <c r="J100" s="3">
-        <v>-3122600</v>
+        <v>-3131600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4206,25 +4206,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-466600</v>
+        <v>-467900</v>
       </c>
       <c r="E101" s="3">
-        <v>219200</v>
+        <v>219800</v>
       </c>
       <c r="F101" s="3">
-        <v>-799600</v>
+        <v>-801900</v>
       </c>
       <c r="G101" s="3">
-        <v>511000</v>
+        <v>512500</v>
       </c>
       <c r="H101" s="3">
-        <v>2121200</v>
+        <v>2127200</v>
       </c>
       <c r="I101" s="3">
-        <v>-528400</v>
+        <v>-529900</v>
       </c>
       <c r="J101" s="3">
-        <v>-298400</v>
+        <v>-299200</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4248,25 +4248,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1420300</v>
+        <v>1424300</v>
       </c>
       <c r="E102" s="3">
-        <v>-3412300</v>
+        <v>-3422100</v>
       </c>
       <c r="F102" s="3">
-        <v>6008700</v>
+        <v>6025900</v>
       </c>
       <c r="G102" s="3">
-        <v>-10436600</v>
+        <v>-10466400</v>
       </c>
       <c r="H102" s="3">
-        <v>12351600</v>
+        <v>12386900</v>
       </c>
       <c r="I102" s="3">
-        <v>-2614900</v>
+        <v>-2622300</v>
       </c>
       <c r="J102" s="3">
-        <v>126900</v>
+        <v>127300</v>
       </c>
       <c r="K102" s="3">
         <v>1220900</v>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>113772800</v>
+        <v>91977300</v>
       </c>
       <c r="E8" s="3">
-        <v>132664400</v>
+        <v>92905600</v>
       </c>
       <c r="F8" s="3">
-        <v>122824700</v>
+        <v>131762200</v>
       </c>
       <c r="G8" s="3">
-        <v>144715100</v>
+        <v>121989400</v>
       </c>
       <c r="H8" s="3">
-        <v>117164400</v>
+        <v>143730900</v>
       </c>
       <c r="I8" s="3">
-        <v>144599800</v>
+        <v>116367600</v>
       </c>
       <c r="J8" s="3">
+        <v>143616400</v>
+      </c>
+      <c r="K8" s="3">
         <v>139088600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>122920600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>133175000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>150327700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>132761400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119444600</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>91614800</v>
+        <v>77465700</v>
       </c>
       <c r="E9" s="3">
-        <v>110428000</v>
+        <v>171470300</v>
       </c>
       <c r="F9" s="3">
-        <v>104727400</v>
+        <v>109677000</v>
       </c>
       <c r="G9" s="3">
-        <v>125923600</v>
+        <v>104015200</v>
       </c>
       <c r="H9" s="3">
-        <v>94691900</v>
+        <v>125067200</v>
       </c>
       <c r="I9" s="3">
-        <v>124107600</v>
+        <v>94047900</v>
       </c>
       <c r="J9" s="3">
+        <v>123263600</v>
+      </c>
+      <c r="K9" s="3">
         <v>117018600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102370000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>113453500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>129281700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>114643300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>99624800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>22158100</v>
+        <v>14511600</v>
       </c>
       <c r="E10" s="3">
-        <v>22236400</v>
+        <v>-78564700</v>
       </c>
       <c r="F10" s="3">
-        <v>18097300</v>
+        <v>22085200</v>
       </c>
       <c r="G10" s="3">
-        <v>18791500</v>
+        <v>17974200</v>
       </c>
       <c r="H10" s="3">
-        <v>22472500</v>
+        <v>18663700</v>
       </c>
       <c r="I10" s="3">
-        <v>20492200</v>
+        <v>22319700</v>
       </c>
       <c r="J10" s="3">
+        <v>20352800</v>
+      </c>
+      <c r="K10" s="3">
         <v>22069900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20550600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19721500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21045900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18118100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19819800</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,51 +962,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1109900</v>
+        <v>296100</v>
       </c>
       <c r="E14" s="3">
-        <v>483100</v>
+        <v>1401700</v>
       </c>
       <c r="F14" s="3">
-        <v>662700</v>
+        <v>479800</v>
       </c>
       <c r="G14" s="3">
-        <v>307900</v>
+        <v>658100</v>
       </c>
       <c r="H14" s="3">
-        <v>8391400</v>
+        <v>305800</v>
       </c>
       <c r="I14" s="3">
-        <v>450500</v>
+        <v>8334400</v>
       </c>
       <c r="J14" s="3">
+        <v>447400</v>
+      </c>
+      <c r="K14" s="3">
         <v>990200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>887700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>760400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1077800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>815800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1426200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1021,18 +1043,21 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>206400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>292300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>103655700</v>
+        <v>82016500</v>
       </c>
       <c r="E17" s="3">
-        <v>122783400</v>
+        <v>84925700</v>
       </c>
       <c r="F17" s="3">
-        <v>116866300</v>
+        <v>121948300</v>
       </c>
       <c r="G17" s="3">
-        <v>138622900</v>
+        <v>116071500</v>
       </c>
       <c r="H17" s="3">
-        <v>115200400</v>
+        <v>137680100</v>
       </c>
       <c r="I17" s="3">
-        <v>136183300</v>
+        <v>114417000</v>
       </c>
       <c r="J17" s="3">
+        <v>135257200</v>
+      </c>
+      <c r="K17" s="3">
         <v>129133500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>114465000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>124764100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>142280800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>126464300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>113979300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10117200</v>
+        <v>9960800</v>
       </c>
       <c r="E18" s="3">
-        <v>9881000</v>
+        <v>7979900</v>
       </c>
       <c r="F18" s="3">
-        <v>5958400</v>
+        <v>9813800</v>
       </c>
       <c r="G18" s="3">
-        <v>6092300</v>
+        <v>5917900</v>
       </c>
       <c r="H18" s="3">
-        <v>1964000</v>
+        <v>6050800</v>
       </c>
       <c r="I18" s="3">
-        <v>8416500</v>
+        <v>1950700</v>
       </c>
       <c r="J18" s="3">
+        <v>8359200</v>
+      </c>
+      <c r="K18" s="3">
         <v>9955000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8455500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8410900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8046800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6297000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5465300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-120800</v>
+        <v>300400</v>
       </c>
       <c r="E20" s="3">
-        <v>627800</v>
+        <v>-161000</v>
       </c>
       <c r="F20" s="3">
-        <v>298100</v>
+        <v>623600</v>
       </c>
       <c r="G20" s="3">
-        <v>810600</v>
+        <v>296100</v>
       </c>
       <c r="H20" s="3">
-        <v>312300</v>
+        <v>805100</v>
       </c>
       <c r="I20" s="3">
-        <v>289400</v>
+        <v>310200</v>
       </c>
       <c r="J20" s="3">
+        <v>287500</v>
+      </c>
+      <c r="K20" s="3">
         <v>237200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>226400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-79600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>167500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>129600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>72800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="3">
-        <v>11461200</v>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>7543800</v>
+        <v>11371700</v>
       </c>
       <c r="G21" s="3">
-        <v>8409100</v>
+        <v>7476900</v>
       </c>
       <c r="H21" s="3">
-        <v>3205600</v>
+        <v>8333600</v>
       </c>
       <c r="I21" s="3">
-        <v>9177700</v>
+        <v>3172600</v>
       </c>
       <c r="J21" s="3">
+        <v>9109500</v>
+      </c>
+      <c r="K21" s="3">
         <v>10927800</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>9504500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7972800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6387300</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>519000</v>
+        <v>658100</v>
       </c>
       <c r="E22" s="3">
-        <v>502700</v>
+        <v>704600</v>
       </c>
       <c r="F22" s="3">
-        <v>955400</v>
+        <v>499300</v>
       </c>
       <c r="G22" s="3">
-        <v>783400</v>
+        <v>948900</v>
       </c>
       <c r="H22" s="3">
-        <v>611500</v>
+        <v>778100</v>
       </c>
       <c r="I22" s="3">
-        <v>342800</v>
+        <v>607400</v>
       </c>
       <c r="J22" s="3">
+        <v>340400</v>
+      </c>
+      <c r="K22" s="3">
         <v>322100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>516300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>555300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>739300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>623700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>386200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9477400</v>
+        <v>9603100</v>
       </c>
       <c r="E23" s="3">
-        <v>10006200</v>
+        <v>7114200</v>
       </c>
       <c r="F23" s="3">
-        <v>5301200</v>
+        <v>9938100</v>
       </c>
       <c r="G23" s="3">
-        <v>6119500</v>
+        <v>5265200</v>
       </c>
       <c r="H23" s="3">
-        <v>1664800</v>
+        <v>6077900</v>
       </c>
       <c r="I23" s="3">
-        <v>8363100</v>
+        <v>1653500</v>
       </c>
       <c r="J23" s="3">
+        <v>8306300</v>
+      </c>
+      <c r="K23" s="3">
         <v>9870200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8165600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7776000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7475100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5802900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5151900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2018400</v>
+        <v>1635100</v>
       </c>
       <c r="E24" s="3">
-        <v>1837800</v>
+        <v>1487000</v>
       </c>
       <c r="F24" s="3">
-        <v>1676800</v>
+        <v>1825300</v>
       </c>
       <c r="G24" s="3">
-        <v>1544000</v>
+        <v>1665400</v>
       </c>
       <c r="H24" s="3">
-        <v>1603900</v>
+        <v>1533500</v>
       </c>
       <c r="I24" s="3">
-        <v>1178400</v>
+        <v>1593000</v>
       </c>
       <c r="J24" s="3">
+        <v>1170400</v>
+      </c>
+      <c r="K24" s="3">
         <v>2652800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1899100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1953800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1748800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1205600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1186700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7458900</v>
+        <v>7968000</v>
       </c>
       <c r="E26" s="3">
-        <v>8168400</v>
+        <v>5627200</v>
       </c>
       <c r="F26" s="3">
-        <v>3624500</v>
+        <v>8112800</v>
       </c>
       <c r="G26" s="3">
-        <v>4575500</v>
+        <v>3599800</v>
       </c>
       <c r="H26" s="3">
-        <v>60900</v>
+        <v>4544300</v>
       </c>
       <c r="I26" s="3">
-        <v>7184700</v>
+        <v>60500</v>
       </c>
       <c r="J26" s="3">
+        <v>7135900</v>
+      </c>
+      <c r="K26" s="3">
         <v>7217400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6266500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5822200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5726200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4597300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3965100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7065000</v>
+        <v>7569200</v>
       </c>
       <c r="E27" s="3">
-        <v>7725500</v>
+        <v>5272700</v>
       </c>
       <c r="F27" s="3">
-        <v>3250200</v>
+        <v>7673000</v>
       </c>
       <c r="G27" s="3">
-        <v>3947600</v>
+        <v>3228100</v>
       </c>
       <c r="H27" s="3">
-        <v>2509200</v>
+        <v>3920800</v>
       </c>
       <c r="I27" s="3">
-        <v>6506800</v>
+        <v>2492100</v>
       </c>
       <c r="J27" s="3">
+        <v>6462600</v>
+      </c>
+      <c r="K27" s="3">
         <v>6529700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5552400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5148000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5021600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4134000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3400500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1537,39 +1597,42 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>-26100</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-465700</v>
+        <v>-25900</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-462500</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-477700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>67700</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>1176200</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>120800</v>
+        <v>-300400</v>
       </c>
       <c r="E32" s="3">
-        <v>-627800</v>
+        <v>161000</v>
       </c>
       <c r="F32" s="3">
-        <v>-298100</v>
+        <v>-623600</v>
       </c>
       <c r="G32" s="3">
-        <v>-810600</v>
+        <v>-296100</v>
       </c>
       <c r="H32" s="3">
-        <v>-312300</v>
+        <v>-805100</v>
       </c>
       <c r="I32" s="3">
-        <v>-289400</v>
+        <v>-310200</v>
       </c>
       <c r="J32" s="3">
+        <v>-287500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-237200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-226400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>79600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-167500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-129600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-72800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7065000</v>
+        <v>7569200</v>
       </c>
       <c r="E33" s="3">
-        <v>7725500</v>
+        <v>5272700</v>
       </c>
       <c r="F33" s="3">
-        <v>3250200</v>
+        <v>7673000</v>
       </c>
       <c r="G33" s="3">
-        <v>3921500</v>
+        <v>3228100</v>
       </c>
       <c r="H33" s="3">
-        <v>2043500</v>
+        <v>3894800</v>
       </c>
       <c r="I33" s="3">
-        <v>6506800</v>
+        <v>2029600</v>
       </c>
       <c r="J33" s="3">
+        <v>6462600</v>
+      </c>
+      <c r="K33" s="3">
         <v>6052000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5620100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5148000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5021600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4134000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4576700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7065000</v>
+        <v>7569200</v>
       </c>
       <c r="E35" s="3">
-        <v>7725500</v>
+        <v>5272700</v>
       </c>
       <c r="F35" s="3">
-        <v>3250200</v>
+        <v>7673000</v>
       </c>
       <c r="G35" s="3">
-        <v>3921500</v>
+        <v>3228100</v>
       </c>
       <c r="H35" s="3">
-        <v>2043500</v>
+        <v>3894800</v>
       </c>
       <c r="I35" s="3">
-        <v>6506800</v>
+        <v>2029600</v>
       </c>
       <c r="J35" s="3">
+        <v>6462600</v>
+      </c>
+      <c r="K35" s="3">
         <v>6052000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5620100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5148000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5021600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4134000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4576700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>28472300</v>
+        <v>26987200</v>
       </c>
       <c r="E41" s="3">
-        <v>27258000</v>
+        <v>28278700</v>
       </c>
       <c r="F41" s="3">
-        <v>30724700</v>
+        <v>27072600</v>
       </c>
       <c r="G41" s="3">
-        <v>23881600</v>
+        <v>30515700</v>
       </c>
       <c r="H41" s="3">
-        <v>34089100</v>
+        <v>23719200</v>
       </c>
       <c r="I41" s="3">
-        <v>26003400</v>
+        <v>33857300</v>
       </c>
       <c r="J41" s="3">
+        <v>25826600</v>
+      </c>
+      <c r="K41" s="3">
         <v>28632300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27799000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24052400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25664500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33539500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36472600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1986,51 +2075,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>44520700</v>
+        <v>12696100</v>
       </c>
       <c r="E43" s="3">
-        <v>40711300</v>
+        <v>45243500</v>
       </c>
       <c r="F43" s="3">
-        <v>40977800</v>
+        <v>40434400</v>
       </c>
       <c r="G43" s="3">
-        <v>42969100</v>
+        <v>40699200</v>
       </c>
       <c r="H43" s="3">
-        <v>45644700</v>
+        <v>42676800</v>
       </c>
       <c r="I43" s="3">
-        <v>32905200</v>
+        <v>45334300</v>
       </c>
       <c r="J43" s="3">
+        <v>32681400</v>
+      </c>
+      <c r="K43" s="3">
         <v>37904000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33546000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31701800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33173000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>53363900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38370700</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,9 +2165,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2112,9 +2210,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2154,135 +2255,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>504961000</v>
+        <v>451686000</v>
       </c>
       <c r="E47" s="3">
-        <v>554716000</v>
+        <v>454044000</v>
       </c>
       <c r="F47" s="3">
-        <v>579780000</v>
+        <v>550943000</v>
       </c>
       <c r="G47" s="3">
-        <v>566400000</v>
+        <v>575837000</v>
       </c>
       <c r="H47" s="3">
-        <v>621675000</v>
+        <v>562548000</v>
       </c>
       <c r="I47" s="3">
-        <v>603064000</v>
+        <v>617447000</v>
       </c>
       <c r="J47" s="3">
+        <v>598963000</v>
+      </c>
+      <c r="K47" s="3">
         <v>619838000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>572538000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>571470000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>723251000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>33638600</v>
+        <v>34190100</v>
       </c>
       <c r="E48" s="3">
-        <v>33511300</v>
+        <v>33409800</v>
       </c>
       <c r="F48" s="3">
-        <v>31038100</v>
+        <v>33283400</v>
       </c>
       <c r="G48" s="3">
-        <v>28478800</v>
+        <v>30827000</v>
       </c>
       <c r="H48" s="3">
-        <v>24523600</v>
+        <v>28285200</v>
       </c>
       <c r="I48" s="3">
-        <v>26637800</v>
+        <v>24356800</v>
       </c>
       <c r="J48" s="3">
+        <v>26456600</v>
+      </c>
+      <c r="K48" s="3">
         <v>24908800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23065500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21744000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22414400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20476600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1655100</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>48443300</v>
+        <v>24299500</v>
       </c>
       <c r="E49" s="3">
-        <v>23355000</v>
+        <v>48113800</v>
       </c>
       <c r="F49" s="3">
-        <v>22866400</v>
+        <v>23196100</v>
       </c>
       <c r="G49" s="3">
-        <v>24643300</v>
+        <v>22710900</v>
       </c>
       <c r="H49" s="3">
-        <v>23733600</v>
+        <v>24475700</v>
       </c>
       <c r="I49" s="3">
-        <v>20196200</v>
+        <v>23572200</v>
       </c>
       <c r="J49" s="3">
+        <v>20058900</v>
+      </c>
+      <c r="K49" s="3">
         <v>21708700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21518700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20947700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>43010600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44897200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30158700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18959100</v>
+        <v>18015300</v>
       </c>
       <c r="E52" s="3">
-        <v>9720000</v>
+        <v>18069300</v>
       </c>
       <c r="F52" s="3">
-        <v>36739700</v>
+        <v>9653900</v>
       </c>
       <c r="G52" s="3">
-        <v>39437100</v>
+        <v>36489800</v>
       </c>
       <c r="H52" s="3">
-        <v>29704000</v>
+        <v>39168900</v>
       </c>
       <c r="I52" s="3">
-        <v>6371900</v>
+        <v>29502000</v>
       </c>
       <c r="J52" s="3">
+        <v>6328600</v>
+      </c>
+      <c r="K52" s="3">
         <v>2738700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5365100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2822200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2875700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3563000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5797400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>692995000</v>
+        <v>696456000</v>
       </c>
       <c r="E54" s="3">
-        <v>843812000</v>
+        <v>689872000</v>
       </c>
       <c r="F54" s="3">
-        <v>875473000</v>
+        <v>838073000</v>
       </c>
       <c r="G54" s="3">
-        <v>849673000</v>
+        <v>869519000</v>
       </c>
       <c r="H54" s="3">
-        <v>1012690000</v>
+        <v>843895000</v>
       </c>
       <c r="I54" s="3">
-        <v>946786000</v>
+        <v>1005800000</v>
       </c>
       <c r="J54" s="3">
+        <v>940347000</v>
+      </c>
+      <c r="K54" s="3">
         <v>971437000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>938520000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>916440000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>903659000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>836525000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>853599000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,8 +2656,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2568,93 +2698,102 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1233900</v>
+        <v>1657800</v>
       </c>
       <c r="E58" s="3">
-        <v>1375400</v>
+        <v>2451000</v>
       </c>
       <c r="F58" s="3">
-        <v>1751800</v>
+        <v>1366000</v>
       </c>
       <c r="G58" s="3">
-        <v>758400</v>
+        <v>1739900</v>
       </c>
       <c r="H58" s="3">
-        <v>1550500</v>
+        <v>753200</v>
       </c>
       <c r="I58" s="3">
-        <v>2530900</v>
+        <v>1540000</v>
       </c>
       <c r="J58" s="3">
+        <v>2513700</v>
+      </c>
+      <c r="K58" s="3">
         <v>4107600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3477600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3038200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6128100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4952000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7362100</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>739256000</v>
+        <v>552946000</v>
       </c>
       <c r="E59" s="3">
-        <v>220912000</v>
+        <v>734206000</v>
       </c>
       <c r="F59" s="3">
-        <v>205751000</v>
+        <v>219409000</v>
       </c>
       <c r="G59" s="3">
-        <v>194923000</v>
+        <v>204352000</v>
       </c>
       <c r="H59" s="3">
-        <v>314725000</v>
+        <v>193598000</v>
       </c>
       <c r="I59" s="3">
-        <v>320914000</v>
+        <v>312585000</v>
       </c>
       <c r="J59" s="3">
+        <v>318732000</v>
+      </c>
+      <c r="K59" s="3">
         <v>322433000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>335035000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>330312000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>346918000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>301801000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55893300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2694,93 +2833,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26316800</v>
+        <v>26011400</v>
       </c>
       <c r="E61" s="3">
-        <v>23116700</v>
+        <v>25491600</v>
       </c>
       <c r="F61" s="3">
-        <v>22669500</v>
+        <v>22959500</v>
       </c>
       <c r="G61" s="3">
-        <v>27009900</v>
+        <v>22515300</v>
       </c>
       <c r="H61" s="3">
-        <v>27191600</v>
+        <v>26826200</v>
       </c>
       <c r="I61" s="3">
-        <v>10352200</v>
+        <v>27006700</v>
       </c>
       <c r="J61" s="3">
+        <v>10281800</v>
+      </c>
+      <c r="K61" s="3">
         <v>9197700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8186800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8114200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8953600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16658900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12232300</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>991300</v>
+        <v>1880400</v>
       </c>
       <c r="E62" s="3">
-        <v>5803900</v>
+        <v>987800</v>
       </c>
       <c r="F62" s="3">
-        <v>16234500</v>
+        <v>5764500</v>
       </c>
       <c r="G62" s="3">
-        <v>15507600</v>
+        <v>16124000</v>
       </c>
       <c r="H62" s="3">
-        <v>14512000</v>
+        <v>15402100</v>
       </c>
       <c r="I62" s="3">
-        <v>16168100</v>
+        <v>14413300</v>
       </c>
       <c r="J62" s="3">
+        <v>16058100</v>
+      </c>
+      <c r="K62" s="3">
         <v>18416100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16430700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17298600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14641500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16362400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4453400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>642865000</v>
+        <v>642876000</v>
       </c>
       <c r="E66" s="3">
-        <v>766410000</v>
+        <v>640082000</v>
       </c>
       <c r="F66" s="3">
-        <v>797553000</v>
+        <v>761198000</v>
       </c>
       <c r="G66" s="3">
-        <v>773618000</v>
+        <v>792129000</v>
       </c>
       <c r="H66" s="3">
-        <v>944761000</v>
+        <v>768357000</v>
       </c>
       <c r="I66" s="3">
-        <v>871043000</v>
+        <v>938336000</v>
       </c>
       <c r="J66" s="3">
+        <v>865119000</v>
+      </c>
+      <c r="K66" s="3">
         <v>894621000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>866074000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>845292000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>840351000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>777665000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>799115000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>69547000</v>
+        <v>35817600</v>
       </c>
       <c r="E72" s="3">
-        <v>34083600</v>
+        <v>69075100</v>
       </c>
       <c r="F72" s="3">
-        <v>53600900</v>
+        <v>33851800</v>
       </c>
       <c r="G72" s="3">
-        <v>49247400</v>
+        <v>53236400</v>
       </c>
       <c r="H72" s="3">
-        <v>41469700</v>
+        <v>48912500</v>
       </c>
       <c r="I72" s="3">
-        <v>52319100</v>
+        <v>41187600</v>
       </c>
       <c r="J72" s="3">
+        <v>51963300</v>
+      </c>
+      <c r="K72" s="3">
         <v>47983000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30534900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27829100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>85131200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>59954100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24918800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>50129900</v>
+        <v>53580000</v>
       </c>
       <c r="E76" s="3">
-        <v>77402000</v>
+        <v>49790000</v>
       </c>
       <c r="F76" s="3">
-        <v>77919900</v>
+        <v>76875600</v>
       </c>
       <c r="G76" s="3">
-        <v>76054900</v>
+        <v>77390000</v>
       </c>
       <c r="H76" s="3">
-        <v>67927900</v>
+        <v>75537700</v>
       </c>
       <c r="I76" s="3">
-        <v>75743700</v>
+        <v>67465900</v>
       </c>
       <c r="J76" s="3">
+        <v>75228600</v>
+      </c>
+      <c r="K76" s="3">
         <v>76816600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72446600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71148100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>63307700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58859400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54484700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7065000</v>
+        <v>7569200</v>
       </c>
       <c r="E81" s="3">
-        <v>7725500</v>
+        <v>5272700</v>
       </c>
       <c r="F81" s="3">
-        <v>3250200</v>
+        <v>7673000</v>
       </c>
       <c r="G81" s="3">
-        <v>3921500</v>
+        <v>3228100</v>
       </c>
       <c r="H81" s="3">
-        <v>2043500</v>
+        <v>3894800</v>
       </c>
       <c r="I81" s="3">
-        <v>6506800</v>
+        <v>2029600</v>
       </c>
       <c r="J81" s="3">
+        <v>6462600</v>
+      </c>
+      <c r="K81" s="3">
         <v>6052000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5620100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5148000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5021600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4134000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4576700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
-        <v>946600</v>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>1279600</v>
+        <v>940200</v>
       </c>
       <c r="G83" s="3">
-        <v>1497200</v>
+        <v>1270900</v>
       </c>
       <c r="H83" s="3">
-        <v>923800</v>
+        <v>1487000</v>
       </c>
       <c r="I83" s="3">
-        <v>469000</v>
+        <v>917500</v>
       </c>
       <c r="J83" s="3">
+        <v>465800</v>
+      </c>
+      <c r="K83" s="3">
         <v>731200</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>1295500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1543800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>848700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8044300</v>
+        <v>7539000</v>
       </c>
       <c r="E89" s="3">
-        <v>10812400</v>
+        <v>8881200</v>
       </c>
       <c r="F89" s="3">
-        <v>24627000</v>
+        <v>10738900</v>
       </c>
       <c r="G89" s="3">
-        <v>8626500</v>
+        <v>24459500</v>
       </c>
       <c r="H89" s="3">
-        <v>8306600</v>
+        <v>8567800</v>
       </c>
       <c r="I89" s="3">
-        <v>17980900</v>
+        <v>8250100</v>
       </c>
       <c r="J89" s="3">
+        <v>17858600</v>
+      </c>
+      <c r="K89" s="3">
         <v>14731800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13659800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5782900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6341100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11545500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20080400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-384100</v>
+        <v>-461500</v>
       </c>
       <c r="E91" s="3">
-        <v>-380800</v>
+        <v>-430100</v>
       </c>
       <c r="F91" s="3">
-        <v>-423300</v>
+        <v>-378200</v>
       </c>
       <c r="G91" s="3">
-        <v>-502700</v>
+        <v>-420400</v>
       </c>
       <c r="H91" s="3">
-        <v>-502700</v>
+        <v>-499300</v>
       </c>
       <c r="I91" s="3">
-        <v>-427600</v>
+        <v>-499300</v>
       </c>
       <c r="J91" s="3">
+        <v>-424700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-513600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-373500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-379600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-416300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-372200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-437800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>511400</v>
+        <v>-1727000</v>
       </c>
       <c r="E94" s="3">
-        <v>-9739600</v>
+        <v>-167500</v>
       </c>
       <c r="F94" s="3">
-        <v>-12438100</v>
+        <v>-9673300</v>
       </c>
       <c r="G94" s="3">
-        <v>-12013700</v>
+        <v>-12353500</v>
       </c>
       <c r="H94" s="3">
-        <v>-2311100</v>
+        <v>-11932000</v>
       </c>
       <c r="I94" s="3">
-        <v>-13423900</v>
+        <v>-2295400</v>
       </c>
       <c r="J94" s="3">
+        <v>-13332600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-11173700</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-13724000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8207600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4020300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3999900</v>
+        <v>-4266600</v>
       </c>
       <c r="E96" s="3">
-        <v>-3796400</v>
+        <v>-3972700</v>
       </c>
       <c r="F96" s="3">
-        <v>-1896600</v>
+        <v>-3770600</v>
       </c>
       <c r="G96" s="3">
-        <v>-3555900</v>
+        <v>-1883700</v>
       </c>
       <c r="H96" s="3">
-        <v>-3714800</v>
+        <v>-3531700</v>
       </c>
       <c r="I96" s="3">
-        <v>-3370900</v>
+        <v>-3689500</v>
       </c>
       <c r="J96" s="3">
+        <v>-3348000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3180500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2364600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2131600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2337400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1968700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2076500</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-6663500</v>
+        <v>-7328200</v>
       </c>
       <c r="E100" s="3">
-        <v>-4714700</v>
+        <v>-6798700</v>
       </c>
       <c r="F100" s="3">
-        <v>-5361100</v>
+        <v>-4682700</v>
       </c>
       <c r="G100" s="3">
-        <v>-7591700</v>
+        <v>-5324600</v>
       </c>
       <c r="H100" s="3">
-        <v>4264300</v>
+        <v>-7540000</v>
       </c>
       <c r="I100" s="3">
-        <v>-6649400</v>
+        <v>4235300</v>
       </c>
       <c r="J100" s="3">
+        <v>-6604200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3131600</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2294300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2905300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6526400</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-467900</v>
+        <v>-163200</v>
       </c>
       <c r="E101" s="3">
-        <v>219800</v>
+        <v>-501400</v>
       </c>
       <c r="F101" s="3">
-        <v>-801900</v>
+        <v>218300</v>
       </c>
       <c r="G101" s="3">
-        <v>512500</v>
+        <v>-796500</v>
       </c>
       <c r="H101" s="3">
-        <v>2127200</v>
+        <v>509000</v>
       </c>
       <c r="I101" s="3">
-        <v>-529900</v>
+        <v>2112800</v>
       </c>
       <c r="J101" s="3">
+        <v>-526300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-299200</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1631600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-368900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>968400</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1424300</v>
+        <v>-1679400</v>
       </c>
       <c r="E102" s="3">
-        <v>-3422100</v>
+        <v>1413600</v>
       </c>
       <c r="F102" s="3">
-        <v>6025900</v>
+        <v>-3398800</v>
       </c>
       <c r="G102" s="3">
-        <v>-10466400</v>
+        <v>5984900</v>
       </c>
       <c r="H102" s="3">
-        <v>12386900</v>
+        <v>-10395300</v>
       </c>
       <c r="I102" s="3">
-        <v>-2622300</v>
+        <v>12302700</v>
       </c>
       <c r="J102" s="3">
+        <v>-2604500</v>
+      </c>
+      <c r="K102" s="3">
         <v>127300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1220900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10313500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11308900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10499700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>91977300</v>
+        <v>94266700</v>
       </c>
       <c r="E8" s="3">
-        <v>92905600</v>
+        <v>95218200</v>
       </c>
       <c r="F8" s="3">
-        <v>131762200</v>
+        <v>135041900</v>
       </c>
       <c r="G8" s="3">
-        <v>121989400</v>
+        <v>125025900</v>
       </c>
       <c r="H8" s="3">
-        <v>143730900</v>
+        <v>147308600</v>
       </c>
       <c r="I8" s="3">
-        <v>116367600</v>
+        <v>119264200</v>
       </c>
       <c r="J8" s="3">
-        <v>143616400</v>
+        <v>147191200</v>
       </c>
       <c r="K8" s="3">
         <v>139088600</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>77465700</v>
+        <v>79393900</v>
       </c>
       <c r="E9" s="3">
-        <v>171470300</v>
+        <v>175738500</v>
       </c>
       <c r="F9" s="3">
-        <v>109677000</v>
+        <v>112407000</v>
       </c>
       <c r="G9" s="3">
-        <v>104015200</v>
+        <v>106604300</v>
       </c>
       <c r="H9" s="3">
-        <v>125067200</v>
+        <v>128180300</v>
       </c>
       <c r="I9" s="3">
-        <v>94047900</v>
+        <v>96388900</v>
       </c>
       <c r="J9" s="3">
-        <v>123263600</v>
+        <v>126331700</v>
       </c>
       <c r="K9" s="3">
         <v>117018600</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>14511600</v>
+        <v>14872900</v>
       </c>
       <c r="E10" s="3">
-        <v>-78564700</v>
+        <v>-80520300</v>
       </c>
       <c r="F10" s="3">
-        <v>22085200</v>
+        <v>22634900</v>
       </c>
       <c r="G10" s="3">
-        <v>17974200</v>
+        <v>18421600</v>
       </c>
       <c r="H10" s="3">
-        <v>18663700</v>
+        <v>19128300</v>
       </c>
       <c r="I10" s="3">
-        <v>22319700</v>
+        <v>22875300</v>
       </c>
       <c r="J10" s="3">
-        <v>20352800</v>
+        <v>20859400</v>
       </c>
       <c r="K10" s="3">
         <v>22069900</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>296100</v>
+        <v>303500</v>
       </c>
       <c r="E14" s="3">
-        <v>1401700</v>
+        <v>1436600</v>
       </c>
       <c r="F14" s="3">
-        <v>479800</v>
+        <v>491800</v>
       </c>
       <c r="G14" s="3">
-        <v>658100</v>
+        <v>674500</v>
       </c>
       <c r="H14" s="3">
-        <v>305800</v>
+        <v>313500</v>
       </c>
       <c r="I14" s="3">
-        <v>8334400</v>
+        <v>8541800</v>
       </c>
       <c r="J14" s="3">
-        <v>447400</v>
+        <v>458500</v>
       </c>
       <c r="K14" s="3">
         <v>990200</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>82016500</v>
+        <v>84058000</v>
       </c>
       <c r="E17" s="3">
-        <v>84925700</v>
+        <v>87039600</v>
       </c>
       <c r="F17" s="3">
-        <v>121948300</v>
+        <v>124983800</v>
       </c>
       <c r="G17" s="3">
-        <v>116071500</v>
+        <v>118960700</v>
       </c>
       <c r="H17" s="3">
-        <v>137680100</v>
+        <v>141107100</v>
       </c>
       <c r="I17" s="3">
-        <v>114417000</v>
+        <v>117264900</v>
       </c>
       <c r="J17" s="3">
-        <v>135257200</v>
+        <v>138623900</v>
       </c>
       <c r="K17" s="3">
         <v>129133500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9960800</v>
+        <v>10208700</v>
       </c>
       <c r="E18" s="3">
-        <v>7979900</v>
+        <v>8178500</v>
       </c>
       <c r="F18" s="3">
-        <v>9813800</v>
+        <v>10058100</v>
       </c>
       <c r="G18" s="3">
-        <v>5917900</v>
+        <v>6065200</v>
       </c>
       <c r="H18" s="3">
-        <v>6050800</v>
+        <v>6201500</v>
       </c>
       <c r="I18" s="3">
-        <v>1950700</v>
+        <v>1999200</v>
       </c>
       <c r="J18" s="3">
-        <v>8359200</v>
+        <v>8567300</v>
       </c>
       <c r="K18" s="3">
         <v>9955000</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300400</v>
+        <v>307900</v>
       </c>
       <c r="E20" s="3">
-        <v>-161000</v>
+        <v>-165000</v>
       </c>
       <c r="F20" s="3">
-        <v>623600</v>
+        <v>639100</v>
       </c>
       <c r="G20" s="3">
-        <v>296100</v>
+        <v>303500</v>
       </c>
       <c r="H20" s="3">
-        <v>805100</v>
+        <v>825200</v>
       </c>
       <c r="I20" s="3">
-        <v>310200</v>
+        <v>317900</v>
       </c>
       <c r="J20" s="3">
-        <v>287500</v>
+        <v>294600</v>
       </c>
       <c r="K20" s="3">
         <v>237200</v>
@@ -1238,19 +1238,19 @@
         <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>11371700</v>
+        <v>11660600</v>
       </c>
       <c r="G21" s="3">
-        <v>7476900</v>
+        <v>7671000</v>
       </c>
       <c r="H21" s="3">
-        <v>8333600</v>
+        <v>8550400</v>
       </c>
       <c r="I21" s="3">
-        <v>3172600</v>
+        <v>3257300</v>
       </c>
       <c r="J21" s="3">
-        <v>9109500</v>
+        <v>9339200</v>
       </c>
       <c r="K21" s="3">
         <v>10927800</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>658100</v>
+        <v>674500</v>
       </c>
       <c r="E22" s="3">
-        <v>704600</v>
+        <v>722200</v>
       </c>
       <c r="F22" s="3">
-        <v>499300</v>
+        <v>511700</v>
       </c>
       <c r="G22" s="3">
-        <v>948900</v>
+        <v>972500</v>
       </c>
       <c r="H22" s="3">
-        <v>778100</v>
+        <v>797500</v>
       </c>
       <c r="I22" s="3">
-        <v>607400</v>
+        <v>622500</v>
       </c>
       <c r="J22" s="3">
-        <v>340400</v>
+        <v>348900</v>
       </c>
       <c r="K22" s="3">
         <v>322100</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9603100</v>
+        <v>9842100</v>
       </c>
       <c r="E23" s="3">
-        <v>7114200</v>
+        <v>7291300</v>
       </c>
       <c r="F23" s="3">
-        <v>9938100</v>
+        <v>10185500</v>
       </c>
       <c r="G23" s="3">
-        <v>5265200</v>
+        <v>5396200</v>
       </c>
       <c r="H23" s="3">
-        <v>6077900</v>
+        <v>6229100</v>
       </c>
       <c r="I23" s="3">
-        <v>1653500</v>
+        <v>1694600</v>
       </c>
       <c r="J23" s="3">
-        <v>8306300</v>
+        <v>8513000</v>
       </c>
       <c r="K23" s="3">
         <v>9870200</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1635100</v>
+        <v>1675800</v>
       </c>
       <c r="E24" s="3">
-        <v>1487000</v>
+        <v>1524100</v>
       </c>
       <c r="F24" s="3">
-        <v>1825300</v>
+        <v>1870700</v>
       </c>
       <c r="G24" s="3">
-        <v>1665400</v>
+        <v>1706800</v>
       </c>
       <c r="H24" s="3">
-        <v>1533500</v>
+        <v>1571700</v>
       </c>
       <c r="I24" s="3">
-        <v>1593000</v>
+        <v>1632600</v>
       </c>
       <c r="J24" s="3">
-        <v>1170400</v>
+        <v>1199500</v>
       </c>
       <c r="K24" s="3">
         <v>2652800</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7968000</v>
+        <v>8166300</v>
       </c>
       <c r="E26" s="3">
-        <v>5627200</v>
+        <v>5767300</v>
       </c>
       <c r="F26" s="3">
-        <v>8112800</v>
+        <v>8314800</v>
       </c>
       <c r="G26" s="3">
-        <v>3599800</v>
+        <v>3689400</v>
       </c>
       <c r="H26" s="3">
-        <v>4544300</v>
+        <v>4657500</v>
       </c>
       <c r="I26" s="3">
-        <v>60500</v>
+        <v>62000</v>
       </c>
       <c r="J26" s="3">
-        <v>7135900</v>
+        <v>7313500</v>
       </c>
       <c r="K26" s="3">
         <v>7217400</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7569200</v>
+        <v>7757600</v>
       </c>
       <c r="E27" s="3">
-        <v>5272700</v>
+        <v>5404000</v>
       </c>
       <c r="F27" s="3">
-        <v>7673000</v>
+        <v>7864000</v>
       </c>
       <c r="G27" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="H27" s="3">
-        <v>3920800</v>
+        <v>4018400</v>
       </c>
       <c r="I27" s="3">
-        <v>2492100</v>
+        <v>2554100</v>
       </c>
       <c r="J27" s="3">
-        <v>6462600</v>
+        <v>6623400</v>
       </c>
       <c r="K27" s="3">
         <v>6529700</v>
@@ -1604,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-25900</v>
+        <v>-26600</v>
       </c>
       <c r="I29" s="3">
-        <v>-462500</v>
+        <v>-474100</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300400</v>
+        <v>-307900</v>
       </c>
       <c r="E32" s="3">
-        <v>161000</v>
+        <v>165000</v>
       </c>
       <c r="F32" s="3">
-        <v>-623600</v>
+        <v>-639100</v>
       </c>
       <c r="G32" s="3">
-        <v>-296100</v>
+        <v>-303500</v>
       </c>
       <c r="H32" s="3">
-        <v>-805100</v>
+        <v>-825200</v>
       </c>
       <c r="I32" s="3">
-        <v>-310200</v>
+        <v>-317900</v>
       </c>
       <c r="J32" s="3">
-        <v>-287500</v>
+        <v>-294600</v>
       </c>
       <c r="K32" s="3">
         <v>-237200</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7569200</v>
+        <v>7757600</v>
       </c>
       <c r="E33" s="3">
-        <v>5272700</v>
+        <v>5404000</v>
       </c>
       <c r="F33" s="3">
-        <v>7673000</v>
+        <v>7864000</v>
       </c>
       <c r="G33" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="H33" s="3">
-        <v>3894800</v>
+        <v>3991800</v>
       </c>
       <c r="I33" s="3">
-        <v>2029600</v>
+        <v>2080100</v>
       </c>
       <c r="J33" s="3">
-        <v>6462600</v>
+        <v>6623400</v>
       </c>
       <c r="K33" s="3">
         <v>6052000</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7569200</v>
+        <v>7757600</v>
       </c>
       <c r="E35" s="3">
-        <v>5272700</v>
+        <v>5404000</v>
       </c>
       <c r="F35" s="3">
-        <v>7673000</v>
+        <v>7864000</v>
       </c>
       <c r="G35" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="H35" s="3">
-        <v>3894800</v>
+        <v>3991800</v>
       </c>
       <c r="I35" s="3">
-        <v>2029600</v>
+        <v>2080100</v>
       </c>
       <c r="J35" s="3">
-        <v>6462600</v>
+        <v>6623400</v>
       </c>
       <c r="K35" s="3">
         <v>6052000</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26987200</v>
+        <v>28115300</v>
       </c>
       <c r="E41" s="3">
-        <v>28278700</v>
+        <v>28982600</v>
       </c>
       <c r="F41" s="3">
-        <v>27072600</v>
+        <v>27746500</v>
       </c>
       <c r="G41" s="3">
-        <v>30515700</v>
+        <v>31275300</v>
       </c>
       <c r="H41" s="3">
-        <v>23719200</v>
+        <v>24309600</v>
       </c>
       <c r="I41" s="3">
-        <v>33857300</v>
+        <v>34700000</v>
       </c>
       <c r="J41" s="3">
-        <v>25826600</v>
+        <v>26469400</v>
       </c>
       <c r="K41" s="3">
         <v>28632300</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12696100</v>
+        <v>13160500</v>
       </c>
       <c r="E43" s="3">
-        <v>45243500</v>
+        <v>46369700</v>
       </c>
       <c r="F43" s="3">
-        <v>40434400</v>
+        <v>41440900</v>
       </c>
       <c r="G43" s="3">
-        <v>40699200</v>
+        <v>41712200</v>
       </c>
       <c r="H43" s="3">
-        <v>42676800</v>
+        <v>43739100</v>
       </c>
       <c r="I43" s="3">
-        <v>45334300</v>
+        <v>46462700</v>
       </c>
       <c r="J43" s="3">
-        <v>32681400</v>
+        <v>33494900</v>
       </c>
       <c r="K43" s="3">
         <v>37904000</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>451686000</v>
+        <v>476728000</v>
       </c>
       <c r="E47" s="3">
-        <v>454044000</v>
+        <v>465346000</v>
       </c>
       <c r="F47" s="3">
-        <v>550943000</v>
+        <v>564657000</v>
       </c>
       <c r="G47" s="3">
-        <v>575837000</v>
+        <v>590170000</v>
       </c>
       <c r="H47" s="3">
-        <v>562548000</v>
+        <v>576550000</v>
       </c>
       <c r="I47" s="3">
-        <v>617447000</v>
+        <v>632816000</v>
       </c>
       <c r="J47" s="3">
-        <v>598963000</v>
+        <v>613872000</v>
       </c>
       <c r="K47" s="3">
         <v>619838000</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34190100</v>
+        <v>35041100</v>
       </c>
       <c r="E48" s="3">
-        <v>33409800</v>
+        <v>34241500</v>
       </c>
       <c r="F48" s="3">
-        <v>33283400</v>
+        <v>34111900</v>
       </c>
       <c r="G48" s="3">
-        <v>30827000</v>
+        <v>31594300</v>
       </c>
       <c r="H48" s="3">
-        <v>28285200</v>
+        <v>28989200</v>
       </c>
       <c r="I48" s="3">
-        <v>24356800</v>
+        <v>24963100</v>
       </c>
       <c r="J48" s="3">
-        <v>26456600</v>
+        <v>27115200</v>
       </c>
       <c r="K48" s="3">
         <v>24908800</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>24299500</v>
+        <v>49808800</v>
       </c>
       <c r="E49" s="3">
-        <v>48113800</v>
+        <v>49311500</v>
       </c>
       <c r="F49" s="3">
-        <v>23196100</v>
+        <v>23773500</v>
       </c>
       <c r="G49" s="3">
-        <v>22710900</v>
+        <v>23276200</v>
       </c>
       <c r="H49" s="3">
-        <v>24475700</v>
+        <v>25084900</v>
       </c>
       <c r="I49" s="3">
-        <v>23572200</v>
+        <v>24159000</v>
       </c>
       <c r="J49" s="3">
-        <v>20058900</v>
+        <v>20558200</v>
       </c>
       <c r="K49" s="3">
         <v>21708700</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18015300</v>
+        <v>3836700</v>
       </c>
       <c r="E52" s="3">
-        <v>18069300</v>
+        <v>18519100</v>
       </c>
       <c r="F52" s="3">
-        <v>9653900</v>
+        <v>9894200</v>
       </c>
       <c r="G52" s="3">
-        <v>36489800</v>
+        <v>37398100</v>
       </c>
       <c r="H52" s="3">
-        <v>39168900</v>
+        <v>40143900</v>
       </c>
       <c r="I52" s="3">
-        <v>29502000</v>
+        <v>30236400</v>
       </c>
       <c r="J52" s="3">
-        <v>6328600</v>
+        <v>6486100</v>
       </c>
       <c r="K52" s="3">
         <v>2738700</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>696456000</v>
+        <v>713721000</v>
       </c>
       <c r="E54" s="3">
-        <v>689872000</v>
+        <v>707044000</v>
       </c>
       <c r="F54" s="3">
-        <v>838073000</v>
+        <v>858934000</v>
       </c>
       <c r="G54" s="3">
-        <v>869519000</v>
+        <v>891163000</v>
       </c>
       <c r="H54" s="3">
-        <v>843895000</v>
+        <v>864901000</v>
       </c>
       <c r="I54" s="3">
-        <v>1005800000</v>
+        <v>1030840000</v>
       </c>
       <c r="J54" s="3">
-        <v>940347000</v>
+        <v>963754000</v>
       </c>
       <c r="K54" s="3">
         <v>971437000</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1657800</v>
+        <v>1699100</v>
       </c>
       <c r="E58" s="3">
-        <v>2451000</v>
+        <v>2512000</v>
       </c>
       <c r="F58" s="3">
-        <v>1366000</v>
+        <v>1400000</v>
       </c>
       <c r="G58" s="3">
-        <v>1739900</v>
+        <v>1783200</v>
       </c>
       <c r="H58" s="3">
-        <v>753200</v>
+        <v>772000</v>
       </c>
       <c r="I58" s="3">
-        <v>1540000</v>
+        <v>1578300</v>
       </c>
       <c r="J58" s="3">
-        <v>2513700</v>
+        <v>2576300</v>
       </c>
       <c r="K58" s="3">
         <v>4107600</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>552946000</v>
+        <v>615729000</v>
       </c>
       <c r="E59" s="3">
-        <v>734206000</v>
+        <v>752481000</v>
       </c>
       <c r="F59" s="3">
-        <v>219409000</v>
+        <v>224871000</v>
       </c>
       <c r="G59" s="3">
-        <v>204352000</v>
+        <v>209438000</v>
       </c>
       <c r="H59" s="3">
-        <v>193598000</v>
+        <v>198417000</v>
       </c>
       <c r="I59" s="3">
-        <v>312585000</v>
+        <v>320366000</v>
       </c>
       <c r="J59" s="3">
-        <v>318732000</v>
+        <v>326666000</v>
       </c>
       <c r="K59" s="3">
         <v>322433000</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26011400</v>
+        <v>27130700</v>
       </c>
       <c r="E61" s="3">
-        <v>25491600</v>
+        <v>26126100</v>
       </c>
       <c r="F61" s="3">
-        <v>22959500</v>
+        <v>23531000</v>
       </c>
       <c r="G61" s="3">
-        <v>22515300</v>
+        <v>23075700</v>
       </c>
       <c r="H61" s="3">
-        <v>26826200</v>
+        <v>27494000</v>
       </c>
       <c r="I61" s="3">
-        <v>27006700</v>
+        <v>27678900</v>
       </c>
       <c r="J61" s="3">
-        <v>10281800</v>
+        <v>10537700</v>
       </c>
       <c r="K61" s="3">
         <v>9197700</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1880400</v>
+        <v>1913900</v>
       </c>
       <c r="E62" s="3">
-        <v>987800</v>
+        <v>1012300</v>
       </c>
       <c r="F62" s="3">
-        <v>5764500</v>
+        <v>5907900</v>
       </c>
       <c r="G62" s="3">
-        <v>16124000</v>
+        <v>16525400</v>
       </c>
       <c r="H62" s="3">
-        <v>15402100</v>
+        <v>15785500</v>
       </c>
       <c r="I62" s="3">
-        <v>14413300</v>
+        <v>14772100</v>
       </c>
       <c r="J62" s="3">
-        <v>16058100</v>
+        <v>16457800</v>
       </c>
       <c r="K62" s="3">
         <v>18416100</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>642876000</v>
+        <v>658807000</v>
       </c>
       <c r="E66" s="3">
-        <v>640082000</v>
+        <v>656015000</v>
       </c>
       <c r="F66" s="3">
-        <v>761198000</v>
+        <v>780145000</v>
       </c>
       <c r="G66" s="3">
-        <v>792129000</v>
+        <v>811846000</v>
       </c>
       <c r="H66" s="3">
-        <v>768357000</v>
+        <v>787483000</v>
       </c>
       <c r="I66" s="3">
-        <v>938336000</v>
+        <v>961693000</v>
       </c>
       <c r="J66" s="3">
-        <v>865119000</v>
+        <v>886653000</v>
       </c>
       <c r="K66" s="3">
         <v>894621000</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35817600</v>
+        <v>36709200</v>
       </c>
       <c r="E72" s="3">
-        <v>69075100</v>
+        <v>70794500</v>
       </c>
       <c r="F72" s="3">
-        <v>33851800</v>
+        <v>34694500</v>
       </c>
       <c r="G72" s="3">
-        <v>53236400</v>
+        <v>54561500</v>
       </c>
       <c r="H72" s="3">
-        <v>48912500</v>
+        <v>50130000</v>
       </c>
       <c r="I72" s="3">
-        <v>41187600</v>
+        <v>42212900</v>
       </c>
       <c r="J72" s="3">
-        <v>51963300</v>
+        <v>53256700</v>
       </c>
       <c r="K72" s="3">
         <v>47983000</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>53580000</v>
+        <v>54913700</v>
       </c>
       <c r="E76" s="3">
-        <v>49790000</v>
+        <v>51029300</v>
       </c>
       <c r="F76" s="3">
-        <v>76875600</v>
+        <v>78789100</v>
       </c>
       <c r="G76" s="3">
-        <v>77390000</v>
+        <v>79316300</v>
       </c>
       <c r="H76" s="3">
-        <v>75537700</v>
+        <v>77417900</v>
       </c>
       <c r="I76" s="3">
-        <v>67465900</v>
+        <v>69145300</v>
       </c>
       <c r="J76" s="3">
-        <v>75228600</v>
+        <v>77101100</v>
       </c>
       <c r="K76" s="3">
         <v>76816600</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7569200</v>
+        <v>7757600</v>
       </c>
       <c r="E81" s="3">
-        <v>5272700</v>
+        <v>5404000</v>
       </c>
       <c r="F81" s="3">
-        <v>7673000</v>
+        <v>7864000</v>
       </c>
       <c r="G81" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="H81" s="3">
-        <v>3894800</v>
+        <v>3991800</v>
       </c>
       <c r="I81" s="3">
-        <v>2029600</v>
+        <v>2080100</v>
       </c>
       <c r="J81" s="3">
-        <v>6462600</v>
+        <v>6623400</v>
       </c>
       <c r="K81" s="3">
         <v>6052000</v>
@@ -3702,19 +3702,19 @@
         <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>940200</v>
+        <v>963600</v>
       </c>
       <c r="G83" s="3">
-        <v>1270900</v>
+        <v>1302500</v>
       </c>
       <c r="H83" s="3">
-        <v>1487000</v>
+        <v>1524100</v>
       </c>
       <c r="I83" s="3">
-        <v>917500</v>
+        <v>940400</v>
       </c>
       <c r="J83" s="3">
-        <v>465800</v>
+        <v>477400</v>
       </c>
       <c r="K83" s="3">
         <v>731200</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7539000</v>
+        <v>7726600</v>
       </c>
       <c r="E89" s="3">
-        <v>8881200</v>
+        <v>9102300</v>
       </c>
       <c r="F89" s="3">
-        <v>10738900</v>
+        <v>11006200</v>
       </c>
       <c r="G89" s="3">
-        <v>24459500</v>
+        <v>25068300</v>
       </c>
       <c r="H89" s="3">
-        <v>8567800</v>
+        <v>8781100</v>
       </c>
       <c r="I89" s="3">
-        <v>8250100</v>
+        <v>8455400</v>
       </c>
       <c r="J89" s="3">
-        <v>17858600</v>
+        <v>18303100</v>
       </c>
       <c r="K89" s="3">
         <v>14731800</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-461500</v>
+        <v>-472900</v>
       </c>
       <c r="E91" s="3">
-        <v>-430100</v>
+        <v>-440800</v>
       </c>
       <c r="F91" s="3">
-        <v>-378200</v>
+        <v>-387700</v>
       </c>
       <c r="G91" s="3">
-        <v>-420400</v>
+        <v>-430900</v>
       </c>
       <c r="H91" s="3">
-        <v>-499300</v>
+        <v>-511700</v>
       </c>
       <c r="I91" s="3">
-        <v>-499300</v>
+        <v>-511700</v>
       </c>
       <c r="J91" s="3">
-        <v>-424700</v>
+        <v>-435300</v>
       </c>
       <c r="K91" s="3">
         <v>-513600</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1727000</v>
+        <v>-1769900</v>
       </c>
       <c r="E94" s="3">
-        <v>-167500</v>
+        <v>-171700</v>
       </c>
       <c r="F94" s="3">
-        <v>-9673300</v>
+        <v>-9914100</v>
       </c>
       <c r="G94" s="3">
-        <v>-12353500</v>
+        <v>-12661000</v>
       </c>
       <c r="H94" s="3">
-        <v>-11932000</v>
+        <v>-12229000</v>
       </c>
       <c r="I94" s="3">
-        <v>-2295400</v>
+        <v>-2352500</v>
       </c>
       <c r="J94" s="3">
-        <v>-13332600</v>
+        <v>-13664500</v>
       </c>
       <c r="K94" s="3">
         <v>-11173700</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4266600</v>
+        <v>-4372800</v>
       </c>
       <c r="E96" s="3">
-        <v>-3972700</v>
+        <v>-4071500</v>
       </c>
       <c r="F96" s="3">
-        <v>-3770600</v>
+        <v>-3864400</v>
       </c>
       <c r="G96" s="3">
-        <v>-1883700</v>
+        <v>-1930500</v>
       </c>
       <c r="H96" s="3">
-        <v>-3531700</v>
+        <v>-3619600</v>
       </c>
       <c r="I96" s="3">
-        <v>-3689500</v>
+        <v>-3781300</v>
       </c>
       <c r="J96" s="3">
-        <v>-3348000</v>
+        <v>-3431300</v>
       </c>
       <c r="K96" s="3">
         <v>-3180500</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-7328200</v>
+        <v>-7510600</v>
       </c>
       <c r="E100" s="3">
-        <v>-6798700</v>
+        <v>-6967900</v>
       </c>
       <c r="F100" s="3">
-        <v>-4682700</v>
+        <v>-4799200</v>
       </c>
       <c r="G100" s="3">
-        <v>-5324600</v>
+        <v>-5457100</v>
       </c>
       <c r="H100" s="3">
-        <v>-7540000</v>
+        <v>-7727700</v>
       </c>
       <c r="I100" s="3">
-        <v>4235300</v>
+        <v>4340700</v>
       </c>
       <c r="J100" s="3">
-        <v>-6604200</v>
+        <v>-6768500</v>
       </c>
       <c r="K100" s="3">
         <v>-3131600</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-163200</v>
+        <v>-167200</v>
       </c>
       <c r="E101" s="3">
-        <v>-501400</v>
+        <v>-513900</v>
       </c>
       <c r="F101" s="3">
-        <v>218300</v>
+        <v>223700</v>
       </c>
       <c r="G101" s="3">
-        <v>-796500</v>
+        <v>-816300</v>
       </c>
       <c r="H101" s="3">
-        <v>509000</v>
+        <v>521700</v>
       </c>
       <c r="I101" s="3">
-        <v>2112800</v>
+        <v>2165400</v>
       </c>
       <c r="J101" s="3">
-        <v>-526300</v>
+        <v>-539400</v>
       </c>
       <c r="K101" s="3">
         <v>-299200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1679400</v>
+        <v>-1721200</v>
       </c>
       <c r="E102" s="3">
-        <v>1413600</v>
+        <v>1448700</v>
       </c>
       <c r="F102" s="3">
-        <v>-3398800</v>
+        <v>-3483400</v>
       </c>
       <c r="G102" s="3">
-        <v>5984900</v>
+        <v>6133900</v>
       </c>
       <c r="H102" s="3">
-        <v>-10395300</v>
+        <v>-10654000</v>
       </c>
       <c r="I102" s="3">
-        <v>12302700</v>
+        <v>12608900</v>
       </c>
       <c r="J102" s="3">
-        <v>-2604500</v>
+        <v>-2669300</v>
       </c>
       <c r="K102" s="3">
         <v>127300</v>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -663,8 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>94266700</v>
+        <v>96331400</v>
       </c>
       <c r="E8" s="3">
-        <v>95218200</v>
+        <v>92757300</v>
       </c>
       <c r="F8" s="3">
-        <v>135041900</v>
+        <v>138941200</v>
       </c>
       <c r="G8" s="3">
-        <v>125025900</v>
+        <v>137427500</v>
       </c>
       <c r="H8" s="3">
-        <v>147308600</v>
+        <v>149376100</v>
       </c>
       <c r="I8" s="3">
-        <v>119264200</v>
+        <v>121851400</v>
       </c>
       <c r="J8" s="3">
-        <v>147191200</v>
+        <v>159212300</v>
       </c>
       <c r="K8" s="3">
         <v>139088600</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>79393900</v>
+        <v>81747500</v>
       </c>
       <c r="E9" s="3">
-        <v>175738500</v>
+        <v>80727800</v>
       </c>
       <c r="F9" s="3">
-        <v>112407000</v>
+        <v>115489600</v>
       </c>
       <c r="G9" s="3">
-        <v>106604300</v>
+        <v>117831200</v>
       </c>
       <c r="H9" s="3">
-        <v>128180300</v>
+        <v>129946100</v>
       </c>
       <c r="I9" s="3">
-        <v>96388900</v>
+        <v>99719500</v>
       </c>
       <c r="J9" s="3">
-        <v>126331700</v>
+        <v>137042500</v>
       </c>
       <c r="K9" s="3">
         <v>117018600</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>14872900</v>
+        <v>14583800</v>
       </c>
       <c r="E10" s="3">
-        <v>-80520300</v>
+        <v>12029500</v>
       </c>
       <c r="F10" s="3">
-        <v>22634900</v>
+        <v>23451600</v>
       </c>
       <c r="G10" s="3">
-        <v>18421600</v>
+        <v>19596300</v>
       </c>
       <c r="H10" s="3">
-        <v>19128300</v>
+        <v>19429900</v>
       </c>
       <c r="I10" s="3">
-        <v>22875300</v>
+        <v>22131900</v>
       </c>
       <c r="J10" s="3">
-        <v>20859400</v>
+        <v>22169800</v>
       </c>
       <c r="K10" s="3">
         <v>22069900</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>303500</v>
+        <v>42000</v>
       </c>
       <c r="E14" s="3">
-        <v>1436600</v>
+        <v>34200</v>
       </c>
       <c r="F14" s="3">
-        <v>491800</v>
+        <v>247900</v>
       </c>
       <c r="G14" s="3">
-        <v>674500</v>
+        <v>112500</v>
       </c>
       <c r="H14" s="3">
-        <v>313500</v>
+        <v>129100</v>
       </c>
       <c r="I14" s="3">
-        <v>8541800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>458500</v>
+        <v>7248700</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>990200</v>
@@ -1020,22 +1020,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>929800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>46600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>134600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>125900</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>136900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>84058000</v>
+        <v>86101500</v>
       </c>
       <c r="E17" s="3">
-        <v>87039600</v>
+        <v>84831700</v>
       </c>
       <c r="F17" s="3">
-        <v>124983800</v>
+        <v>127872200</v>
       </c>
       <c r="G17" s="3">
-        <v>118960700</v>
+        <v>130767000</v>
       </c>
       <c r="H17" s="3">
-        <v>141107100</v>
+        <v>142692200</v>
       </c>
       <c r="I17" s="3">
-        <v>117264900</v>
+        <v>112537200</v>
       </c>
       <c r="J17" s="3">
-        <v>138623900</v>
+        <v>149931600</v>
       </c>
       <c r="K17" s="3">
         <v>129133500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10208700</v>
+        <v>10229900</v>
       </c>
       <c r="E18" s="3">
-        <v>8178500</v>
+        <v>7925600</v>
       </c>
       <c r="F18" s="3">
-        <v>10058100</v>
+        <v>11069000</v>
       </c>
       <c r="G18" s="3">
-        <v>6065200</v>
+        <v>6660600</v>
       </c>
       <c r="H18" s="3">
-        <v>6201500</v>
+        <v>6683900</v>
       </c>
       <c r="I18" s="3">
-        <v>1999200</v>
+        <v>9314200</v>
       </c>
       <c r="J18" s="3">
-        <v>8567300</v>
+        <v>9280700</v>
       </c>
       <c r="K18" s="3">
         <v>9955000</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>307900</v>
+        <v>-307300</v>
       </c>
       <c r="E20" s="3">
-        <v>-165000</v>
+        <v>159200</v>
       </c>
       <c r="F20" s="3">
-        <v>639100</v>
+        <v>-163800</v>
       </c>
       <c r="G20" s="3">
-        <v>303500</v>
+        <v>-485600</v>
       </c>
       <c r="H20" s="3">
-        <v>825200</v>
+        <v>-565600</v>
       </c>
       <c r="I20" s="3">
-        <v>317900</v>
+        <v>-328600</v>
       </c>
       <c r="J20" s="3">
-        <v>294600</v>
+        <v>-326600</v>
       </c>
       <c r="K20" s="3">
         <v>237200</v>
@@ -1231,26 +1231,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>10537200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8696200</v>
       </c>
       <c r="F21" s="3">
-        <v>11660600</v>
+        <v>11279400</v>
       </c>
       <c r="G21" s="3">
-        <v>7671000</v>
+        <v>7280700</v>
       </c>
       <c r="H21" s="3">
-        <v>8550400</v>
+        <v>7292100</v>
       </c>
       <c r="I21" s="3">
-        <v>3257300</v>
+        <v>9768700</v>
       </c>
       <c r="J21" s="3">
-        <v>9339200</v>
+        <v>9744200</v>
       </c>
       <c r="K21" s="3">
         <v>10927800</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>674500</v>
+        <v>673200</v>
       </c>
       <c r="E22" s="3">
-        <v>722200</v>
+        <v>696800</v>
       </c>
       <c r="F22" s="3">
-        <v>511700</v>
+        <v>525400</v>
       </c>
       <c r="G22" s="3">
-        <v>972500</v>
+        <v>1074000</v>
       </c>
       <c r="H22" s="3">
-        <v>797500</v>
+        <v>808000</v>
       </c>
       <c r="I22" s="3">
-        <v>622500</v>
+        <v>643500</v>
       </c>
       <c r="J22" s="3">
-        <v>348900</v>
+        <v>378200</v>
       </c>
       <c r="K22" s="3">
         <v>322100</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9842100</v>
+        <v>9822000</v>
       </c>
       <c r="E23" s="3">
-        <v>7291300</v>
+        <v>7035400</v>
       </c>
       <c r="F23" s="3">
-        <v>10185500</v>
+        <v>10459500</v>
       </c>
       <c r="G23" s="3">
-        <v>5396200</v>
+        <v>5959600</v>
       </c>
       <c r="H23" s="3">
-        <v>6229100</v>
+        <v>6312400</v>
       </c>
       <c r="I23" s="3">
-        <v>1694600</v>
+        <v>1750600</v>
       </c>
       <c r="J23" s="3">
-        <v>8513000</v>
+        <v>9229100</v>
       </c>
       <c r="K23" s="3">
         <v>9870200</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1675800</v>
+        <v>1672400</v>
       </c>
       <c r="E24" s="3">
-        <v>1524100</v>
+        <v>1470600</v>
       </c>
       <c r="F24" s="3">
-        <v>1870700</v>
+        <v>1920800</v>
       </c>
       <c r="G24" s="3">
-        <v>1706800</v>
+        <v>1885000</v>
       </c>
       <c r="H24" s="3">
-        <v>1571700</v>
+        <v>1592400</v>
       </c>
       <c r="I24" s="3">
-        <v>1632600</v>
+        <v>1687700</v>
       </c>
       <c r="J24" s="3">
-        <v>1199500</v>
+        <v>1300400</v>
       </c>
       <c r="K24" s="3">
         <v>2652800</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8166300</v>
+        <v>8149700</v>
       </c>
       <c r="E26" s="3">
-        <v>5767300</v>
+        <v>5564800</v>
       </c>
       <c r="F26" s="3">
-        <v>8314800</v>
+        <v>8538600</v>
       </c>
       <c r="G26" s="3">
-        <v>3689400</v>
+        <v>4074600</v>
       </c>
       <c r="H26" s="3">
-        <v>4657500</v>
+        <v>4720000</v>
       </c>
       <c r="I26" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="J26" s="3">
-        <v>7313500</v>
+        <v>7928700</v>
       </c>
       <c r="K26" s="3">
         <v>7217400</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7757600</v>
+        <v>7741800</v>
       </c>
       <c r="E27" s="3">
-        <v>5404000</v>
+        <v>5214300</v>
       </c>
       <c r="F27" s="3">
-        <v>7864000</v>
+        <v>8074600</v>
       </c>
       <c r="G27" s="3">
-        <v>3308400</v>
+        <v>3653800</v>
       </c>
       <c r="H27" s="3">
-        <v>4018400</v>
+        <v>4043300</v>
       </c>
       <c r="I27" s="3">
-        <v>2554100</v>
+        <v>2150200</v>
       </c>
       <c r="J27" s="3">
-        <v>6623400</v>
+        <v>7180600</v>
       </c>
       <c r="K27" s="3">
         <v>6529700</v>
@@ -1591,23 +1591,23 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-26600</v>
+        <v>-26900</v>
       </c>
       <c r="I29" s="3">
-        <v>-474100</v>
+        <v>-490000</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-307900</v>
+        <v>307300</v>
       </c>
       <c r="E32" s="3">
-        <v>165000</v>
+        <v>-159200</v>
       </c>
       <c r="F32" s="3">
-        <v>-639100</v>
+        <v>163800</v>
       </c>
       <c r="G32" s="3">
-        <v>-303500</v>
+        <v>485600</v>
       </c>
       <c r="H32" s="3">
-        <v>-825200</v>
+        <v>565600</v>
       </c>
       <c r="I32" s="3">
-        <v>-317900</v>
+        <v>328600</v>
       </c>
       <c r="J32" s="3">
-        <v>-294600</v>
+        <v>326600</v>
       </c>
       <c r="K32" s="3">
         <v>-237200</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7757600</v>
+        <v>7946300</v>
       </c>
       <c r="E33" s="3">
-        <v>5404000</v>
+        <v>5408800</v>
       </c>
       <c r="F33" s="3">
-        <v>7864000</v>
+        <v>8295200</v>
       </c>
       <c r="G33" s="3">
-        <v>3308400</v>
+        <v>3870300</v>
       </c>
       <c r="H33" s="3">
-        <v>3991800</v>
+        <v>4328400</v>
       </c>
       <c r="I33" s="3">
-        <v>2080100</v>
+        <v>2450200</v>
       </c>
       <c r="J33" s="3">
-        <v>6623400</v>
+        <v>7455600</v>
       </c>
       <c r="K33" s="3">
         <v>6052000</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7757600</v>
+        <v>7946300</v>
       </c>
       <c r="E35" s="3">
-        <v>5404000</v>
+        <v>5408800</v>
       </c>
       <c r="F35" s="3">
-        <v>7864000</v>
+        <v>8295200</v>
       </c>
       <c r="G35" s="3">
-        <v>3308400</v>
+        <v>3870300</v>
       </c>
       <c r="H35" s="3">
-        <v>3991800</v>
+        <v>4328400</v>
       </c>
       <c r="I35" s="3">
-        <v>2080100</v>
+        <v>2450200</v>
       </c>
       <c r="J35" s="3">
-        <v>6623400</v>
+        <v>7455600</v>
       </c>
       <c r="K35" s="3">
         <v>6052000</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>28115300</v>
+        <v>27602500</v>
       </c>
       <c r="E41" s="3">
-        <v>28982600</v>
+        <v>27965200</v>
       </c>
       <c r="F41" s="3">
-        <v>27746500</v>
+        <v>28489700</v>
       </c>
       <c r="G41" s="3">
-        <v>31275300</v>
+        <v>34540700</v>
       </c>
       <c r="H41" s="3">
-        <v>24309600</v>
+        <v>25424800</v>
       </c>
       <c r="I41" s="3">
-        <v>34700000</v>
+        <v>35870200</v>
       </c>
       <c r="J41" s="3">
-        <v>26469400</v>
+        <v>28696000</v>
       </c>
       <c r="K41" s="3">
         <v>28632300</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>17809200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>16943500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>390200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>343400</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1211400</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1421700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13160500</v>
+        <v>8817300</v>
       </c>
       <c r="E43" s="3">
-        <v>46369700</v>
+        <v>8296500</v>
       </c>
       <c r="F43" s="3">
-        <v>41440900</v>
+        <v>31951600</v>
       </c>
       <c r="G43" s="3">
-        <v>41712200</v>
+        <v>34824500</v>
       </c>
       <c r="H43" s="3">
-        <v>43739100</v>
+        <v>32899800</v>
       </c>
       <c r="I43" s="3">
-        <v>46462700</v>
+        <v>37071200</v>
       </c>
       <c r="J43" s="3">
-        <v>33494900</v>
+        <v>29050200</v>
       </c>
       <c r="K43" s="3">
         <v>37904000</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>56847600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>60878500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>62076700</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>85450800</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>69305400</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>70944600</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>29674600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>111076600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>114083600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>122519000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>155206100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>127973300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>145097300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>88842500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>476728000</v>
+        <v>407063100</v>
       </c>
       <c r="E47" s="3">
-        <v>465346000</v>
+        <v>387322900</v>
       </c>
       <c r="F47" s="3">
-        <v>564657000</v>
+        <v>537890400</v>
       </c>
       <c r="G47" s="3">
-        <v>590170000</v>
+        <v>603858100</v>
       </c>
       <c r="H47" s="3">
-        <v>576550000</v>
+        <v>544237500</v>
       </c>
       <c r="I47" s="3">
-        <v>632816000</v>
+        <v>574008500</v>
       </c>
       <c r="J47" s="3">
-        <v>613872000</v>
+        <v>587239400</v>
       </c>
       <c r="K47" s="3">
         <v>619838000</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>35041100</v>
+        <v>2315700</v>
       </c>
       <c r="E48" s="3">
-        <v>34241500</v>
+        <v>2384300</v>
       </c>
       <c r="F48" s="3">
-        <v>34111900</v>
+        <v>2778300</v>
       </c>
       <c r="G48" s="3">
-        <v>31594300</v>
+        <v>3240400</v>
       </c>
       <c r="H48" s="3">
-        <v>28989200</v>
+        <v>3224100</v>
       </c>
       <c r="I48" s="3">
-        <v>24963100</v>
+        <v>1830800</v>
       </c>
       <c r="J48" s="3">
-        <v>27115200</v>
+        <v>1657100</v>
       </c>
       <c r="K48" s="3">
         <v>24908800</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>49808800</v>
+        <v>24403700</v>
       </c>
       <c r="E49" s="3">
-        <v>49311500</v>
+        <v>23534300</v>
       </c>
       <c r="F49" s="3">
-        <v>23773500</v>
+        <v>45727300</v>
       </c>
       <c r="G49" s="3">
-        <v>23276200</v>
+        <v>47454400</v>
       </c>
       <c r="H49" s="3">
-        <v>25084900</v>
+        <v>46189000</v>
       </c>
       <c r="I49" s="3">
-        <v>24159000</v>
+        <v>57607100</v>
       </c>
       <c r="J49" s="3">
-        <v>20558200</v>
+        <v>52032900</v>
       </c>
       <c r="K49" s="3">
         <v>21708700</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3836700</v>
+        <v>130189000</v>
       </c>
       <c r="E52" s="3">
-        <v>18519100</v>
+        <v>117291900</v>
       </c>
       <c r="F52" s="3">
-        <v>9894200</v>
+        <v>135250800</v>
       </c>
       <c r="G52" s="3">
-        <v>37398100</v>
+        <v>134026900</v>
       </c>
       <c r="H52" s="3">
-        <v>40143900</v>
+        <v>116514400</v>
       </c>
       <c r="I52" s="3">
-        <v>30236400</v>
+        <v>211150700</v>
       </c>
       <c r="J52" s="3">
-        <v>6486100</v>
+        <v>240506700</v>
       </c>
       <c r="K52" s="3">
         <v>2738700</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>713721000</v>
+        <v>712334500</v>
       </c>
       <c r="E54" s="3">
-        <v>707044000</v>
+        <v>682224000</v>
       </c>
       <c r="F54" s="3">
-        <v>858934000</v>
+        <v>881941300</v>
       </c>
       <c r="G54" s="3">
-        <v>891163000</v>
+        <v>984206700</v>
       </c>
       <c r="H54" s="3">
-        <v>864901000</v>
+        <v>876307900</v>
       </c>
       <c r="I54" s="3">
-        <v>1030840000</v>
+        <v>1065600000</v>
       </c>
       <c r="J54" s="3">
-        <v>963754000</v>
+        <v>1044822300</v>
       </c>
       <c r="K54" s="3">
         <v>971437000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>136797500</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>137630600</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>121384800</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>120587400</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>84339600</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1699100</v>
+        <v>39207500</v>
       </c>
       <c r="E58" s="3">
-        <v>2512000</v>
+        <v>42824600</v>
       </c>
       <c r="F58" s="3">
-        <v>1400000</v>
+        <v>34943700</v>
       </c>
       <c r="G58" s="3">
-        <v>1783200</v>
+        <v>43394500</v>
       </c>
       <c r="H58" s="3">
-        <v>772000</v>
+        <v>33142200</v>
       </c>
       <c r="I58" s="3">
-        <v>1578300</v>
+        <v>32309400</v>
       </c>
       <c r="J58" s="3">
-        <v>2576300</v>
+        <v>35220900</v>
       </c>
       <c r="K58" s="3">
         <v>4107600</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>615729000</v>
+        <v>38892500</v>
       </c>
       <c r="E59" s="3">
-        <v>752481000</v>
+        <v>43947800</v>
       </c>
       <c r="F59" s="3">
-        <v>224871000</v>
+        <v>46850900</v>
       </c>
       <c r="G59" s="3">
-        <v>209438000</v>
+        <v>79570600</v>
       </c>
       <c r="H59" s="3">
-        <v>198417000</v>
+        <v>70953900</v>
       </c>
       <c r="I59" s="3">
-        <v>320366000</v>
+        <v>82269300</v>
       </c>
       <c r="J59" s="3">
-        <v>326666000</v>
+        <v>45411900</v>
       </c>
       <c r="K59" s="3">
         <v>322433000</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>78201600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>86879300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>218697800</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>260694800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>225595300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>235301100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>165090100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>27130700</v>
+        <v>26605500</v>
       </c>
       <c r="E61" s="3">
-        <v>26126100</v>
+        <v>25207900</v>
       </c>
       <c r="F61" s="3">
-        <v>23531000</v>
+        <v>34654800</v>
       </c>
       <c r="G61" s="3">
-        <v>23075700</v>
+        <v>36839100</v>
       </c>
       <c r="H61" s="3">
-        <v>27494000</v>
+        <v>33284700</v>
       </c>
       <c r="I61" s="3">
-        <v>27678900</v>
+        <v>34989700</v>
       </c>
       <c r="J61" s="3">
-        <v>10537700</v>
+        <v>20276200</v>
       </c>
       <c r="K61" s="3">
         <v>9197700</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1913900</v>
+        <v>535408400</v>
       </c>
       <c r="E62" s="3">
-        <v>1012300</v>
+        <v>504977000</v>
       </c>
       <c r="F62" s="3">
-        <v>5907900</v>
+        <v>519645200</v>
       </c>
       <c r="G62" s="3">
-        <v>16525400</v>
+        <v>563962100</v>
       </c>
       <c r="H62" s="3">
-        <v>15785500</v>
+        <v>508018200</v>
       </c>
       <c r="I62" s="3">
-        <v>14772100</v>
+        <v>688387900</v>
       </c>
       <c r="J62" s="3">
-        <v>16457800</v>
+        <v>740721700</v>
       </c>
       <c r="K62" s="3">
         <v>18416100</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>658807000</v>
+        <v>646024100</v>
       </c>
       <c r="E66" s="3">
-        <v>656015000</v>
+        <v>622920800</v>
       </c>
       <c r="F66" s="3">
-        <v>780145000</v>
+        <v>787571900</v>
       </c>
       <c r="G66" s="3">
-        <v>811846000</v>
+        <v>879746800</v>
       </c>
       <c r="H66" s="3">
-        <v>787483000</v>
+        <v>782914400</v>
       </c>
       <c r="I66" s="3">
-        <v>961693000</v>
+        <v>973948900</v>
       </c>
       <c r="J66" s="3">
-        <v>886653000</v>
+        <v>943930100</v>
       </c>
       <c r="K66" s="3">
         <v>894621000</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>36709200</v>
+        <v>36634200</v>
       </c>
       <c r="E72" s="3">
-        <v>70794500</v>
+        <v>32172700</v>
       </c>
       <c r="F72" s="3">
-        <v>34694500</v>
+        <v>28092800</v>
       </c>
       <c r="G72" s="3">
-        <v>54561500</v>
+        <v>24801200</v>
       </c>
       <c r="H72" s="3">
-        <v>50130000</v>
+        <v>21655300</v>
       </c>
       <c r="I72" s="3">
-        <v>42212900</v>
+        <v>22635700</v>
       </c>
       <c r="J72" s="3">
-        <v>53256700</v>
+        <v>29747800</v>
       </c>
       <c r="K72" s="3">
         <v>47983000</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>54913700</v>
+        <v>54801600</v>
       </c>
       <c r="E76" s="3">
-        <v>51029300</v>
+        <v>49238000</v>
       </c>
       <c r="F76" s="3">
-        <v>78789100</v>
+        <v>80899600</v>
       </c>
       <c r="G76" s="3">
-        <v>79316300</v>
+        <v>87596300</v>
       </c>
       <c r="H76" s="3">
-        <v>77417900</v>
+        <v>78439000</v>
       </c>
       <c r="I76" s="3">
-        <v>69145300</v>
+        <v>71477000</v>
       </c>
       <c r="J76" s="3">
-        <v>77101100</v>
+        <v>83586700</v>
       </c>
       <c r="K76" s="3">
         <v>76816600</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7757600</v>
+        <v>7946300</v>
       </c>
       <c r="E81" s="3">
-        <v>5404000</v>
+        <v>5408800</v>
       </c>
       <c r="F81" s="3">
-        <v>7864000</v>
+        <v>8295200</v>
       </c>
       <c r="G81" s="3">
-        <v>3308400</v>
+        <v>3870300</v>
       </c>
       <c r="H81" s="3">
-        <v>3991800</v>
+        <v>4328400</v>
       </c>
       <c r="I81" s="3">
-        <v>2080100</v>
+        <v>2450200</v>
       </c>
       <c r="J81" s="3">
-        <v>6623400</v>
+        <v>7455600</v>
       </c>
       <c r="K81" s="3">
         <v>6052000</v>
@@ -3695,26 +3695,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>-745000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-1000300</v>
       </c>
       <c r="F83" s="3">
-        <v>963600</v>
+        <v>709700</v>
       </c>
       <c r="G83" s="3">
-        <v>1302500</v>
+        <v>1230600</v>
       </c>
       <c r="H83" s="3">
-        <v>1524100</v>
+        <v>1380300</v>
       </c>
       <c r="I83" s="3">
-        <v>940400</v>
+        <v>837000</v>
       </c>
       <c r="J83" s="3">
-        <v>477400</v>
+        <v>391500</v>
       </c>
       <c r="K83" s="3">
         <v>731200</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7726600</v>
+        <v>7115100</v>
       </c>
       <c r="E89" s="3">
-        <v>9102300</v>
+        <v>9303200</v>
       </c>
       <c r="F89" s="3">
-        <v>11006200</v>
+        <v>7421800</v>
       </c>
       <c r="G89" s="3">
-        <v>25068300</v>
+        <v>31234300</v>
       </c>
       <c r="H89" s="3">
-        <v>8781100</v>
+        <v>9905700</v>
       </c>
       <c r="I89" s="3">
-        <v>8455400</v>
+        <v>8740600</v>
       </c>
       <c r="J89" s="3">
-        <v>18303100</v>
+        <v>19842700</v>
       </c>
       <c r="K89" s="3">
         <v>14731800</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-472900</v>
+        <v>-472000</v>
       </c>
       <c r="E91" s="3">
-        <v>-440800</v>
+        <v>-425400</v>
       </c>
       <c r="F91" s="3">
-        <v>-387700</v>
+        <v>-398000</v>
       </c>
       <c r="G91" s="3">
-        <v>-430900</v>
+        <v>-475800</v>
       </c>
       <c r="H91" s="3">
-        <v>-511700</v>
+        <v>-518500</v>
       </c>
       <c r="I91" s="3">
-        <v>-511700</v>
+        <v>-529000</v>
       </c>
       <c r="J91" s="3">
-        <v>-435300</v>
+        <v>-471900</v>
       </c>
       <c r="K91" s="3">
         <v>-513600</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1769900</v>
+        <v>-1766300</v>
       </c>
       <c r="E94" s="3">
-        <v>-171700</v>
+        <v>-165700</v>
       </c>
       <c r="F94" s="3">
-        <v>-9914100</v>
+        <v>-10179700</v>
       </c>
       <c r="G94" s="3">
-        <v>-12661000</v>
+        <v>-13982900</v>
       </c>
       <c r="H94" s="3">
-        <v>-12229000</v>
+        <v>-12390300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2352500</v>
+        <v>-2431900</v>
       </c>
       <c r="J94" s="3">
-        <v>-13664500</v>
+        <v>-14813900</v>
       </c>
       <c r="K94" s="3">
         <v>-11173700</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4372800</v>
+        <v>4640200</v>
       </c>
       <c r="E96" s="3">
-        <v>-4071500</v>
+        <v>4238500</v>
       </c>
       <c r="F96" s="3">
-        <v>-3864400</v>
+        <v>4269300</v>
       </c>
       <c r="G96" s="3">
-        <v>-1930500</v>
+        <v>2132100</v>
       </c>
       <c r="H96" s="3">
-        <v>-3619600</v>
+        <v>3667400</v>
       </c>
       <c r="I96" s="3">
-        <v>-3781300</v>
+        <v>3907700</v>
       </c>
       <c r="J96" s="3">
-        <v>-3431300</v>
+        <v>3720000</v>
       </c>
       <c r="K96" s="3">
         <v>-3180500</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-7510600</v>
+        <v>-7495300</v>
       </c>
       <c r="E100" s="3">
-        <v>-6967900</v>
+        <v>-6723300</v>
       </c>
       <c r="F100" s="3">
-        <v>-4799200</v>
+        <v>-4927800</v>
       </c>
       <c r="G100" s="3">
-        <v>-5457100</v>
+        <v>-6026900</v>
       </c>
       <c r="H100" s="3">
-        <v>-7727700</v>
+        <v>-7829600</v>
       </c>
       <c r="I100" s="3">
-        <v>4340700</v>
+        <v>4487100</v>
       </c>
       <c r="J100" s="3">
-        <v>-6768500</v>
+        <v>-7337900</v>
       </c>
       <c r="K100" s="3">
         <v>-3131600</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-167200</v>
+        <v>-166900</v>
       </c>
       <c r="E101" s="3">
-        <v>-513900</v>
+        <v>-495900</v>
       </c>
       <c r="F101" s="3">
-        <v>223700</v>
+        <v>229700</v>
       </c>
       <c r="G101" s="3">
-        <v>-816300</v>
+        <v>-901500</v>
       </c>
       <c r="H101" s="3">
-        <v>521700</v>
+        <v>528600</v>
       </c>
       <c r="I101" s="3">
-        <v>2165400</v>
+        <v>2239500</v>
       </c>
       <c r="J101" s="3">
-        <v>-539400</v>
+        <v>-584800</v>
       </c>
       <c r="K101" s="3">
         <v>-299200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1721200</v>
+        <v>-2313500</v>
       </c>
       <c r="E102" s="3">
-        <v>1448700</v>
+        <v>1918300</v>
       </c>
       <c r="F102" s="3">
-        <v>-3483400</v>
+        <v>-7455900</v>
       </c>
       <c r="G102" s="3">
-        <v>6133900</v>
+        <v>10322900</v>
       </c>
       <c r="H102" s="3">
-        <v>-10654000</v>
+        <v>-9785700</v>
       </c>
       <c r="I102" s="3">
-        <v>12608900</v>
+        <v>13035300</v>
       </c>
       <c r="J102" s="3">
-        <v>-2669300</v>
+        <v>-2893900</v>
       </c>
       <c r="K102" s="3">
         <v>127300</v>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>84697200</v>
+      </c>
+      <c r="E8" s="3">
         <v>96331400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>92757300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>138941200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>137427500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149376100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>121851400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>159212300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>139088600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>122920600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>133175000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>150327700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>132761400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>119444600</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>69037200</v>
+      </c>
+      <c r="E9" s="3">
         <v>81747500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>80727800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>115489600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>117831200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>129946100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99719500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>137042500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>117018600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102370000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>113453500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>129281700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>114643300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>99624800</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15660000</v>
+      </c>
+      <c r="E10" s="3">
         <v>14583800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12029500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23451600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19596300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19429900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22131900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22169800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22069900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20550600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19721500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21045900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18118100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19819800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E14" s="3">
         <v>42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>34200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>247900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>112500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>129100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7248700</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>990200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>887700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>760400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1077800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>815800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1426200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>135600</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>929800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>134600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>125900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>136900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>206400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>292300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>72774600</v>
+      </c>
+      <c r="E17" s="3">
         <v>86101500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>84831700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>127872200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>130767000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>142692200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>112537200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>149931600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129133500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>114465000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124764100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>142280800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>126464300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>113979300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11922600</v>
+      </c>
+      <c r="E18" s="3">
         <v>10229900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7925600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11069000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6660600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6683900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9314200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9280700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9955000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8455500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8410900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8046800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6297000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5465300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-227800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-307300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>159200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-163800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-485600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-565600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-328600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-326600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>237200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>226400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-79600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>167500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>129600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>72800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12286000</v>
+      </c>
+      <c r="E21" s="3">
         <v>10537200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8696200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11279400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7280700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7292100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9768700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9744200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10927800</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>9504500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7972800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6387300</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>981500</v>
+      </c>
+      <c r="E22" s="3">
         <v>673200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>696800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>525400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1074000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>808000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>643500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>378200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>322100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>516300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>555300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>739300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>623700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>386200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11105700</v>
+      </c>
+      <c r="E23" s="3">
         <v>9822000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7035400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10459500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5959600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6312400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1750600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9229100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9870200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8165600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7776000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7475100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5802900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5151900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2756000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1672400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1470600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1920800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1885000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1592400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1687700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2652800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1899100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1953800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1748800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1205600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1186700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8349700</v>
+      </c>
+      <c r="E26" s="3">
         <v>8149700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5564800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8538600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4074600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4720000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>63000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7928700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7217400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6266500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5822200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5726200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4597300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3965100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7956300</v>
+      </c>
+      <c r="E27" s="3">
         <v>7741800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5214300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8074600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3653800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4043300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2150200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7180600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6529700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5552400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5148000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5021600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4134000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3400500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1604,35 +1664,38 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-26900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-490000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-477700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>67700</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>1176200</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>227800</v>
+      </c>
+      <c r="E32" s="3">
         <v>307300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-159200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>163800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>485600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>565600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>328600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>326600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-237200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-226400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>79600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-167500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-129600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-72800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8164400</v>
+      </c>
+      <c r="E33" s="3">
         <v>7946300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5408800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8295200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3870300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4328400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2450200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7455600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6052000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5620100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5148000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5021600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4134000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4576700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8164400</v>
+      </c>
+      <c r="E35" s="3">
         <v>7946300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5408800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8295200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3870300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4328400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2450200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7455600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6052000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5620100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5148000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5021600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4134000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4576700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,80 +2074,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19670800</v>
+      </c>
+      <c r="E41" s="3">
         <v>27602500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>27965200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28489700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34540700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25424800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35870200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28696000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28632300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27799000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24052400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25664500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33539500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36472600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>17809200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16943500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>390200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>343400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1211400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1421700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2078,54 +2167,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>51972300</v>
+      </c>
+      <c r="E43" s="3">
         <v>8817300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8296500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31951600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34824500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>32899800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>37071200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29050200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37904000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33546000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31701800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33173000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>53363900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>38370700</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,36 +2263,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4658900</v>
+      </c>
+      <c r="E45" s="3">
         <v>56847600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>60878500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62076700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>85450800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>69305400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>70944600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29674600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2213,36 +2311,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76301900</v>
+      </c>
+      <c r="E46" s="3">
         <v>111076600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>114083600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>122519000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155206100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127973300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>145097300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>88842500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2258,144 +2359,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>453670200</v>
+      </c>
+      <c r="E47" s="3">
         <v>407063100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>387322900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>537890400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>603858100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>544237500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>574008500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>587239400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>619838000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>572538000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>571470000</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>723251000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>2315700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2384300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2778300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3240400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3224100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1830800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1657100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24908800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23065500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21744000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22414400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20476600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1655100</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23294300</v>
+      </c>
+      <c r="E49" s="3">
         <v>24403700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23534300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>45727300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47454400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46189000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>57607100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>52032900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21708700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21518700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20947700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>43010600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>44897200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30158700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>123615300</v>
+      </c>
+      <c r="E52" s="3">
         <v>130189000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>117291900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>135250800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>134026900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116514400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>211150700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>240506700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2738700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5365100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2822200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2875700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3563000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5797400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>676881700</v>
+      </c>
+      <c r="E54" s="3">
         <v>712334500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>682224000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>881941300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>984206700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>876307900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1065600000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1044822300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>971437000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>938520000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>916440000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>903659000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>836525000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>853599000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,35 +2786,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>8800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>136797500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>137630600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>121384800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>120587400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84339600</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -2701,126 +2831,135 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>39207500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42824600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34943700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43394500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>33142200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32309400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35220900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4107600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3477600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3038200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6128100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4952000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7362100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1449400</v>
+      </c>
+      <c r="E59" s="3">
         <v>38892500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43947800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46850900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79570600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>70953900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>82269300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45411900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>322433000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>335035000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>330312000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>346918000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>301801000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>55893300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1449400</v>
+      </c>
+      <c r="E60" s="3">
         <v>78201600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86879300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>218697800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>260694800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>225595300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>235301100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>165090100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2836,99 +2975,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14908400</v>
+      </c>
+      <c r="E61" s="3">
         <v>26605500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25207900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34654800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36839100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33284700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34989700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20276200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9197700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8186800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8114200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8953600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16658900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12232300</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>606273900</v>
+      </c>
+      <c r="E62" s="3">
         <v>535408400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>504977000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>519645200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>563962100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>508018200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>688387900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>740721700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18416100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16430700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17298600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14641500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16362400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4453400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>622631700</v>
+      </c>
+      <c r="E66" s="3">
         <v>646024100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>622920800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>787571900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>879746800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>782914400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>973948900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>943930100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>894621000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>866074000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>845292000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>840351000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>777665000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>799115000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37685100</v>
+      </c>
+      <c r="E72" s="3">
         <v>36634200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>32172700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28092800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24801200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21655300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22635700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29747800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47983000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30534900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27829100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>85131200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>59954100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24918800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51661700</v>
+      </c>
+      <c r="E76" s="3">
         <v>54801600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49238000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80899600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>87596300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>78439000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71477000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83586700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>76816600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72446600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71148100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63307700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58859400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54484700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8164400</v>
+      </c>
+      <c r="E81" s="3">
         <v>7946300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5408800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8295200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3870300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4328400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2450200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7455600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6052000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5620100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5148000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5021600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4134000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4576700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>-745000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-1000300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>709700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1230600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1380300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>837000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>391500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>731200</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>1295500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1543800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>848700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>7115100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9303200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7421800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31234300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9905700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8740600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19842700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14731800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13659800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5782900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6341100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11545500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20080400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-472000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-425400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-398000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-475800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-518500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-529000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-471900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-513600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-373500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-379600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-416300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-372200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-437800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1766300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-165700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10179700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13982900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12390300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2431900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14813900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11173700</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-13724000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8207600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4020300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>4640200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4238500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4269300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2132100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3667400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3907700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3720000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3180500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2364600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2131600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2337400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1968700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2076500</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7495300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6723300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4927800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6026900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7829600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4487100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7337900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3131600</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-2294300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2905300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6526400</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>-166900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-495900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>229700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-901500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>528600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2239500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-584800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-299200</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1631600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-368900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>968400</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2313500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1918300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7455900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10322900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9785700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13035300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2893900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>127300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1220900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10313500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11308900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10499700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -731,10 +731,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>84697200</v>
+        <v>94476700</v>
       </c>
       <c r="E8" s="3">
-        <v>96331400</v>
+        <v>94746300</v>
       </c>
       <c r="F8" s="3">
         <v>92757300</v>
@@ -779,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>69037200</v>
+        <v>80786800</v>
       </c>
       <c r="E9" s="3">
         <v>81747500</v>
@@ -827,10 +827,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>15660000</v>
+        <v>13689800</v>
       </c>
       <c r="E10" s="3">
-        <v>14583800</v>
+        <v>12998800</v>
       </c>
       <c r="F10" s="3">
         <v>12029500</v>
@@ -991,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>63200</v>
+        <v>37300</v>
       </c>
       <c r="E14" s="3">
         <v>42000</v>
@@ -1039,7 +1039,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>135600</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1104,10 +1104,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>72774600</v>
+        <v>83660800</v>
       </c>
       <c r="E17" s="3">
-        <v>86101500</v>
+        <v>84979600</v>
       </c>
       <c r="F17" s="3">
         <v>84831700</v>
@@ -1152,10 +1152,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11922600</v>
+        <v>10815800</v>
       </c>
       <c r="E18" s="3">
-        <v>10229900</v>
+        <v>9766800</v>
       </c>
       <c r="F18" s="3">
         <v>7925600</v>
@@ -1220,10 +1220,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-227800</v>
+        <v>-180100</v>
       </c>
       <c r="E20" s="3">
-        <v>-307300</v>
+        <v>-274100</v>
       </c>
       <c r="F20" s="3">
         <v>159200</v>
@@ -1268,10 +1268,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12286000</v>
+        <v>10996000</v>
       </c>
       <c r="E21" s="3">
-        <v>10537200</v>
+        <v>10040900</v>
       </c>
       <c r="F21" s="3">
         <v>8696200</v>
@@ -1316,10 +1316,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>981500</v>
+        <v>628400</v>
       </c>
       <c r="E22" s="3">
-        <v>673200</v>
+        <v>675400</v>
       </c>
       <c r="F22" s="3">
         <v>696800</v>
@@ -1364,10 +1364,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11105700</v>
+        <v>10330300</v>
       </c>
       <c r="E23" s="3">
-        <v>9822000</v>
+        <v>9323500</v>
       </c>
       <c r="F23" s="3">
         <v>7035400</v>
@@ -1412,10 +1412,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2756000</v>
+        <v>2545800</v>
       </c>
       <c r="E24" s="3">
-        <v>1672400</v>
+        <v>1546400</v>
       </c>
       <c r="F24" s="3">
         <v>1470600</v>
@@ -1508,10 +1508,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8349700</v>
+        <v>7784400</v>
       </c>
       <c r="E26" s="3">
-        <v>8149700</v>
+        <v>7777200</v>
       </c>
       <c r="F26" s="3">
         <v>5564800</v>
@@ -1652,10 +1652,10 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>574600</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>372500</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1796,10 +1796,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>227800</v>
+        <v>180100</v>
       </c>
       <c r="E32" s="3">
-        <v>307300</v>
+        <v>274100</v>
       </c>
       <c r="F32" s="3">
         <v>-159200</v>
@@ -2081,10 +2081,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19670800</v>
+        <v>19658300</v>
       </c>
       <c r="E41" s="3">
-        <v>27602500</v>
+        <v>28057900</v>
       </c>
       <c r="F41" s="3">
         <v>27965200</v>
@@ -2129,13 +2129,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>50579800</v>
       </c>
       <c r="E42" s="3">
-        <v>17809200</v>
+        <v>54979600</v>
       </c>
       <c r="F42" s="3">
-        <v>16943500</v>
+        <v>51559300</v>
       </c>
       <c r="G42" s="3">
         <v>1100</v>
@@ -2177,10 +2177,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>51972300</v>
+        <v>7445900</v>
       </c>
       <c r="E43" s="3">
-        <v>8817300</v>
+        <v>8964300</v>
       </c>
       <c r="F43" s="3">
         <v>8296500</v>
@@ -2273,10 +2273,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4658900</v>
+        <v>40887300</v>
       </c>
       <c r="E45" s="3">
-        <v>56847600</v>
+        <v>42566600</v>
       </c>
       <c r="F45" s="3">
         <v>60878500</v>
@@ -2321,13 +2321,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>76301900</v>
+        <v>118571300</v>
       </c>
       <c r="E46" s="3">
-        <v>111076600</v>
+        <v>134568400</v>
       </c>
       <c r="F46" s="3">
-        <v>114083600</v>
+        <v>148699400</v>
       </c>
       <c r="G46" s="3">
         <v>122519000</v>
@@ -2369,13 +2369,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>453670200</v>
+        <v>371256900</v>
       </c>
       <c r="E47" s="3">
-        <v>407063100</v>
+        <v>383660900</v>
       </c>
       <c r="F47" s="3">
-        <v>387322900</v>
+        <v>352707100</v>
       </c>
       <c r="G47" s="3">
         <v>537890400</v>
@@ -2416,8 +2416,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>2290100</v>
       </c>
       <c r="E48" s="3">
         <v>2315700</v>
@@ -2465,10 +2465,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>23294300</v>
+        <v>22940300</v>
       </c>
       <c r="E49" s="3">
-        <v>24403700</v>
+        <v>24402600</v>
       </c>
       <c r="F49" s="3">
         <v>23534300</v>
@@ -2609,10 +2609,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>123615300</v>
+        <v>128981300</v>
       </c>
       <c r="E52" s="3">
-        <v>130189000</v>
+        <v>130190100</v>
       </c>
       <c r="F52" s="3">
         <v>117291900</v>
@@ -2705,10 +2705,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>676881700</v>
+        <v>676842300</v>
       </c>
       <c r="E54" s="3">
-        <v>712334500</v>
+        <v>712263700</v>
       </c>
       <c r="F54" s="3">
         <v>682224000</v>
@@ -2792,8 +2792,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>6200</v>
       </c>
       <c r="E57" s="3">
         <v>8800</v>
@@ -2841,7 +2841,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>38899500</v>
       </c>
       <c r="E58" s="3">
         <v>39207500</v>
@@ -2889,10 +2889,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1449400</v>
+        <v>22452600</v>
       </c>
       <c r="E59" s="3">
-        <v>38892500</v>
+        <v>25271400</v>
       </c>
       <c r="F59" s="3">
         <v>43947800</v>
@@ -2937,10 +2937,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1449400</v>
+        <v>61450500</v>
       </c>
       <c r="E60" s="3">
-        <v>78201600</v>
+        <v>64580500</v>
       </c>
       <c r="F60" s="3">
         <v>86879300</v>
@@ -2985,7 +2985,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14908400</v>
+        <v>25434300</v>
       </c>
       <c r="E61" s="3">
         <v>26605500</v>
@@ -3033,10 +3033,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>606273900</v>
+        <v>521780700</v>
       </c>
       <c r="E62" s="3">
-        <v>535408400</v>
+        <v>548925600</v>
       </c>
       <c r="F62" s="3">
         <v>504977000</v>
@@ -3225,10 +3225,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>622631700</v>
+        <v>614079100</v>
       </c>
       <c r="E66" s="3">
-        <v>646024100</v>
+        <v>645953400</v>
       </c>
       <c r="F66" s="3">
         <v>622920800</v>
@@ -3485,7 +3485,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>37685100</v>
+        <v>37771000</v>
       </c>
       <c r="E72" s="3">
         <v>36634200</v>
@@ -3677,7 +3677,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>51661700</v>
+        <v>51706200</v>
       </c>
       <c r="E76" s="3">
         <v>54801600</v>
@@ -3893,11 +3893,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>-581800</v>
       </c>
       <c r="E83" s="3">
-        <v>-745000</v>
+        <v>-621200</v>
       </c>
       <c r="F83" s="3">
         <v>-1000300</v>
@@ -4181,11 +4181,11 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>12297300</v>
       </c>
       <c r="E89" s="3">
-        <v>7115100</v>
+        <v>4412500</v>
       </c>
       <c r="F89" s="3">
         <v>9303200</v>
@@ -4249,11 +4249,11 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-492800</v>
       </c>
       <c r="E91" s="3">
-        <v>-472000</v>
+        <v>-463100</v>
       </c>
       <c r="F91" s="3">
         <v>-425400</v>
@@ -4393,11 +4393,11 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-11646100</v>
       </c>
       <c r="E94" s="3">
-        <v>-1766300</v>
+        <v>-1757500</v>
       </c>
       <c r="F94" s="3">
         <v>-165700</v>
@@ -4462,10 +4462,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>4927000</v>
       </c>
       <c r="E96" s="3">
-        <v>4640200</v>
+        <v>4624700</v>
       </c>
       <c r="F96" s="3">
         <v>4238500</v>
@@ -4653,11 +4653,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-7594000</v>
       </c>
       <c r="E100" s="3">
-        <v>-7495300</v>
+        <v>-4802700</v>
       </c>
       <c r="F100" s="3">
         <v>-6723300</v>
@@ -4701,8 +4701,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>289900</v>
       </c>
       <c r="E101" s="3">
         <v>-166900</v>
@@ -4750,10 +4750,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-6652900</v>
       </c>
       <c r="E102" s="3">
-        <v>-2313500</v>
+        <v>-2314600</v>
       </c>
       <c r="F102" s="3">
         <v>1918300</v>

--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>111178800</v>
+      </c>
+      <c r="E8" s="3">
         <v>94476700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>94746300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>92757300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>138941200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>137427500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149376100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>121851400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>159212300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139088600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>122920600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>133175000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>150327700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>132761400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>119444600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>95053400</v>
+      </c>
+      <c r="E9" s="3">
         <v>80786800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>81747500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80727800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>115489600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>117831200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>129946100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99719500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>137042500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117018600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>102370000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>113453500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>129281700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>114643300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>99624800</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16125400</v>
+      </c>
+      <c r="E10" s="3">
         <v>13689800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12998800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12029500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23451600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19596300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19429900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22131900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22169800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22069900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20550600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19721500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21045900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18118100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19819800</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,57 +1000,63 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E14" s="3">
         <v>37300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>34200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>247900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>112500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>129100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7248700</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>990200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>887700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>760400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1077800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>815800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1426200</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,44 +1067,47 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>929800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>46600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>134600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>125900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>136900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>206400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>292300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>98946800</v>
+      </c>
+      <c r="E17" s="3">
         <v>83660800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>84979600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>84831700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127872200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>130767000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>142692200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>112537200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149931600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129133500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>114465000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124764100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>142280800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>126464300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>113979300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12232000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10815800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9766800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7925600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11069000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6660600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6683900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9314200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9280700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9955000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8455500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8410900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8046800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6297000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5465300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-302900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-180100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-274100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>159200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-163800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-485600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-565600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-328600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-326600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>237200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>226400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-79600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>167500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>129600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>72800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12534900</v>
+      </c>
+      <c r="E21" s="3">
         <v>10996000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10040900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8696200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11279400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7280700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7292100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9768700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9744200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10927800</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>9504500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7972800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6387300</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>736200</v>
+      </c>
+      <c r="E22" s="3">
         <v>628400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>675400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>696800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>525400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1074000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>808000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>643500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>378200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>322100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>516300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>555300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>739300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>623700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>386200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11740000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10330300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9323500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7035400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10459500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5959600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6312400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1750600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9229100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9870200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8165600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7776000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7475100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5802900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5151900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2779100</v>
+      </c>
+      <c r="E24" s="3">
         <v>2545800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1546400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1470600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1920800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1885000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1592400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1687700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2652800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1899100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1953800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1748800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1205600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1186700</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8960900</v>
+      </c>
+      <c r="E26" s="3">
         <v>7784400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7777200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5564800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8538600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4074600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4720000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>63000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7928700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7217400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6266500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5822200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5726200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4597300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3965100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11298600</v>
+      </c>
+      <c r="E27" s="3">
         <v>7956300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7741800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5214300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8074600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3653800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4043300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2150200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7180600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6529700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5552400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5148000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5021600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4134000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3400500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,21 +1702,24 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>2758000</v>
+      </c>
+      <c r="E29" s="3">
         <v>574600</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>372500</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -1667,35 +1727,38 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-26900</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-490000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-477700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>67700</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>1176200</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>302900</v>
+      </c>
+      <c r="E32" s="3">
         <v>180100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>274100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-159200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>163800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>485600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>565600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>328600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>326600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-237200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-226400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>79600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-167500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-129600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-72800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11502900</v>
+      </c>
+      <c r="E33" s="3">
         <v>8164400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7946300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5408800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8295200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3870300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4328400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2450200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7455600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6052000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5620100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5148000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5021600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4134000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4576700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11502900</v>
+      </c>
+      <c r="E35" s="3">
         <v>8164400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7946300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5408800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8295200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3870300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4328400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2450200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7455600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6052000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5620100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5148000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5021600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4134000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4576700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,86 +2160,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26123000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19658300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28057900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27965200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28489700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34540700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25424800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35870200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28696000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28632300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27799000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24052400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25664500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33539500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36472600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>54956000</v>
+      </c>
+      <c r="E42" s="3">
         <v>50579800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>54979600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>51559300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>390200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>343400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1211400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1421700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2170,57 +2259,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8771900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7445900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8964300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8296500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31951600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34824500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32899800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37071200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29050200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37904000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33546000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31701800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33173000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>53363900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>38370700</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,39 +2361,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37708100</v>
+      </c>
+      <c r="E45" s="3">
         <v>40887300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42566600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>60878500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>62076700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>85450800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>69305400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>70944600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29674600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2314,39 +2412,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127559000</v>
+      </c>
+      <c r="E46" s="3">
         <v>118571300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>134568400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>148699400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>122519000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>155206100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>127973300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>145097300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>88842500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2362,153 +2463,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>403320400</v>
+      </c>
+      <c r="E47" s="3">
         <v>371256900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>383660900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>352707100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>537890400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>603858100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>544237500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>574008500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>587239400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>619838000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>572538000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>571470000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>723251000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2520800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2290100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2315700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2384300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2778300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3240400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3224100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1830800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1657100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24908800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23065500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21744000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22414400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20476600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1655100</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22940300</v>
+        <v>25625200</v>
       </c>
       <c r="E49" s="3">
+        <v>22941300</v>
+      </c>
+      <c r="F49" s="3">
         <v>24402600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23534300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>45727300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>47454400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46189000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57607100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>52032900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21708700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21518700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20947700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>43010600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>44897200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>30158700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>151822200</v>
+      </c>
+      <c r="E52" s="3">
         <v>128981300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>130190100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>117291900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>135250800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>134026900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116514400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>211150700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>240506700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2738700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5365100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2822200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2875700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3563000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5797400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>746200500</v>
+      </c>
+      <c r="E54" s="3">
         <v>676842300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>712263700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>682224000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>881941300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>984206700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>876307900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1065600000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1044822300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>971437000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>938520000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>916440000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>903659000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>836525000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>853599000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,38 +2916,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>136797500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>137630600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>121384800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120587400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>84339600</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -2834,135 +2964,144 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38899500</v>
+        <v>44793900</v>
       </c>
       <c r="E58" s="3">
+        <v>35226200</v>
+      </c>
+      <c r="F58" s="3">
         <v>39207500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42824600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>34943700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43394500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33142200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32309400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>35220900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4107600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3477600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3038200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6128100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7362100</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21231700</v>
+      </c>
+      <c r="E59" s="3">
         <v>22452600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25271400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>43947800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46850900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>79570600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>70953900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82269300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45411900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>322433000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>335035000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>330312000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>346918000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>301801000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>55893300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>61450500</v>
+        <v>66177100</v>
       </c>
       <c r="E60" s="3">
+        <v>57777200</v>
+      </c>
+      <c r="F60" s="3">
         <v>64580500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86879300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>218697800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>260694800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>225595300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>235301100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>165090100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2978,105 +3117,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25434300</v>
+        <v>26056100</v>
       </c>
       <c r="E61" s="3">
+        <v>29107600</v>
+      </c>
+      <c r="F61" s="3">
         <v>26605500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25207900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34654800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36839100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33284700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34989700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20276200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9197700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8186800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8114200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8953600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16658900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12232300</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>585458500</v>
+      </c>
+      <c r="E62" s="3">
         <v>521780700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>548925600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>504977000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>519645200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>563962100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>508018200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>688387900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>740721700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18416100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16430700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17298600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14641500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16362400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4453400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>683787700</v>
+      </c>
+      <c r="E66" s="3">
         <v>614079100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>645953400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>622920800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>787571900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>879746800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>782914400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>973948900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>943930100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>894621000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>866074000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>845292000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>840351000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>777665000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>799115000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48622800</v>
+      </c>
+      <c r="E72" s="3">
         <v>37771000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>36634200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32172700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28092800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24801200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21655300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22635700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29747800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47983000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30534900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27829100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>85131200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>59954100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24918800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>55384500</v>
+      </c>
+      <c r="E76" s="3">
         <v>51706200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>54801600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49238000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>80899600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>87596300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>78439000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71477000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83586700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>76816600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72446600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71148100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>63307700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58859400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>54484700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11502900</v>
+      </c>
+      <c r="E81" s="3">
         <v>8164400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7946300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5408800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8295200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3870300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4328400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2450200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7455600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6052000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5620100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5148000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5021600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4134000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4576700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-964000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-717500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-772600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-1000300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>709700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1230600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1380300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>837000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>391500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>731200</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>1295500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1543800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>848700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26617400</v>
+      </c>
+      <c r="E89" s="3">
         <v>12297300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4412500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9303200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7421800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31234300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9905700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8740600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19842700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14731800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13659800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5782900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6341100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11545500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20080400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-502500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-492800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-463100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-425400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-398000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-475800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-518500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-529000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-471900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-513600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-373500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-379600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-416300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-372200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-437800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12854300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11646100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1757500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-165700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10179700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13982900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12390300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2431900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14813900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11173700</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-13724000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8207600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4020300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5846000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4927000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4624700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4238500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4269300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2132100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3667400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3907700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3720000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3180500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2364600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2131600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2337400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1968700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2076500</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10560100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7594000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4802700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6723300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4927800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6026900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7829600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4487100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7337900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3131600</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2294300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2905300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6526400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E101" s="3">
         <v>289900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-166900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-495900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>229700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-901500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>528600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2239500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-584800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-299200</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1631600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-368900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>968400</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3355600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6652900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2314600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1918300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7455900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10322900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9785700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13035300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2893900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>127300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1220900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10313500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11308900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10499700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
